--- a/Results/Phase 2/Carbon dioxide/carbon dioxide ozone depletion results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide ozone depletion results.xlsx
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.041687027012961e-09</v>
+        <v>5.041687027012849e-09</v>
       </c>
       <c r="C2" t="n">
         <v>2.738017716852822e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.011922815112068e-08</v>
+        <v>2.01192281511206e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.797523957435387e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.387220216318095e-09</v>
+        <v>9.387220216318075e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.193023618600532e-09</v>
+        <v>6.193023618600646e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.988491646006094e-08</v>
+        <v>1.988491646006088e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.127656981690578e-08</v>
+        <v>1.127656981690568e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.33899636898424e-08</v>
+        <v>1.33899636898422e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>7.264493637989496e-09</v>
+        <v>7.264493637989401e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>3.960454710443298e-09</v>
+        <v>3.96045471044321e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>8.386247543208083e-09</v>
+        <v>8.386247543208057e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.453812299852148e-08</v>
+        <v>3.453812299852138e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>8.132611379392862e-09</v>
+        <v>8.132611379392785e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.317539604448889e-08</v>
+        <v>1.317539604448883e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.597963825961554e-08</v>
+        <v>1.597963825961545e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.552102159136516e-08</v>
+        <v>1.552102159136507e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.294747494082383e-08</v>
+        <v>1.294747494082374e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>9.135667033206419e-09</v>
+        <v>9.135667033206272e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.355392601111713e-08</v>
+        <v>1.355392601111694e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.251693114226355e-08</v>
+        <v>1.251693114226351e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>7.377162662465731e-08</v>
+        <v>7.377162662465722e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.550063376711034e-08</v>
+        <v>1.550063376711025e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.420445194514992e-08</v>
+        <v>1.420445194514984e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.185439297461989e-08</v>
+        <v>1.18543929746198e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.121678528366099e-08</v>
+        <v>1.121678528366088e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.42606865810597e-09</v>
+        <v>7.426068658105957e-09</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.285385297616818e-09</v>
+        <v>3.285385297616695e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>3.983281934529783e-09</v>
+        <v>3.983281934529764e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>3.906033026303086e-09</v>
+        <v>3.906033026303128e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.529555070852799e-09</v>
+        <v>3.529555070852787e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.349891105413197e-09</v>
+        <v>3.349891105413181e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.034728375842223e-09</v>
+        <v>4.034728375842244e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>3.906033026303086e-09</v>
+        <v>3.906033026303128e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.906033026303086e-09</v>
+        <v>3.906033026303128e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.874862931039268e-09</v>
+        <v>3.874862931039199e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.906033026303086e-09</v>
+        <v>3.906033026303128e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>3.906033026303086e-09</v>
+        <v>3.906033026303128e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.853421988264471e-09</v>
+        <v>3.853421988264456e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.424927203967549e-09</v>
+        <v>3.42492720396753e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.557139260326333e-09</v>
+        <v>3.557139260326318e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.524730890722906e-09</v>
+        <v>3.524730890722969e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.163413853842984e-09</v>
+        <v>3.163413853842841e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>3.906033026303086e-09</v>
+        <v>3.906033026303128e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>3.906033026303086e-09</v>
+        <v>3.906033026303128e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>3.906033026303086e-09</v>
+        <v>3.906033026303128e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.599342258948183e-09</v>
+        <v>3.599342258948129e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.659169586463224e-09</v>
+        <v>3.65916958646318e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.906154999447405e-09</v>
+        <v>3.906154999447327e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.220297450247498e-09</v>
+        <v>3.220297450247435e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.5166951409572e-09</v>
+        <v>4.51669514095719e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.27385644757465e-09</v>
+        <v>3.273856447574603e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.906033026303086e-09</v>
+        <v>3.906033026303128e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.524508077750004e-09</v>
+        <v>4.524508077749986e-09</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.320578944517605e-08</v>
+        <v>6.320578944517591e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.139699937824407e-08</v>
+        <v>7.139699937824404e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.870137613548649e-08</v>
+        <v>6.870137613548646e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.789068307824084e-08</v>
+        <v>6.789068307824088e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.476923204743118e-08</v>
+        <v>6.476923204743113e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.362543811313295e-08</v>
+        <v>6.362543811313286e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.861597227552207e-08</v>
+        <v>6.861597227552197e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.547833100840187e-08</v>
+        <v>6.547833100840173e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.917611492472297e-08</v>
+        <v>6.917611492472276e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.401597635336394e-08</v>
+        <v>6.40159763533638e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.281169296225732e-08</v>
+        <v>6.28116929622571e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.439140754705021e-08</v>
+        <v>6.439140754705009e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.395689399215244e-08</v>
+        <v>7.395689399215239e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.433239507615223e-08</v>
+        <v>6.43323950761521e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.617043087121258e-08</v>
+        <v>6.61704308712124e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.719254422955159e-08</v>
+        <v>6.719254422955146e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.702538383932317e-08</v>
+        <v>6.702538383932302e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.608735630531137e-08</v>
+        <v>6.608735630531118e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.469799708349313e-08</v>
+        <v>6.469799708349294e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.630840059912543e-08</v>
+        <v>6.630840059912523e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.554753676363888e-08</v>
+        <v>8.554753676363894e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>8.825704536081944e-08</v>
+        <v>8.825704536081928e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.701795271678819e-08</v>
+        <v>6.701795271678821e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.654550966321903e-08</v>
+        <v>6.654550966321893e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.568894076424655e-08</v>
+        <v>6.568894076424644e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.54565402480595e-08</v>
+        <v>6.545654024805937e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.405590272158149e-08</v>
+        <v>6.40559027215813e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.256563808834718e-08</v>
+        <v>6.256563808834711e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.286910580566656e-08</v>
+        <v>6.286910580566648e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.279185689743983e-08</v>
+        <v>6.279185689743978e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.262540070650642e-08</v>
+        <v>6.262540070650644e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.256869648040416e-08</v>
+        <v>6.256869648040402e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.283876484112975e-08</v>
+        <v>6.28387648411297e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.279185689743983e-08</v>
+        <v>6.279185689743978e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.279185689743983e-08</v>
+        <v>6.279185689743978e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.570797243009322e-08</v>
+        <v>6.570797243009325e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.279185689743983e-08</v>
+        <v>6.279185689743978e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.279185689743983e-08</v>
+        <v>6.279185689743978e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.273924585939827e-08</v>
+        <v>6.27392458593981e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.261649947462847e-08</v>
+        <v>6.261649947462825e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.266468921665878e-08</v>
+        <v>6.266468921665868e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.265287674649671e-08</v>
+        <v>6.265287674649654e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.252118092935261e-08</v>
+        <v>6.25211809293525e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.279185689743983e-08</v>
+        <v>6.279185689743978e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.279185689743983e-08</v>
+        <v>6.279185689743978e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.279185689743983e-08</v>
+        <v>6.279185689743978e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.268007171408366e-08</v>
+        <v>6.268007171408378e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.231898668963732e-08</v>
+        <v>8.231898668963751e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.279190135521871e-08</v>
+        <v>6.279190135521852e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.254191433228136e-08</v>
+        <v>6.254191433228115e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.301443606747461e-08</v>
+        <v>6.301443606747457e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.256143595788562e-08</v>
+        <v>6.256143595788544e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.279185689743983e-08</v>
+        <v>6.279185689743978e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.299831796188612e-08</v>
+        <v>6.299831796188615e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.401692317407441e-09</v>
+        <v>3.401692317407387e-09</v>
       </c>
       <c r="C6" t="n">
         <v>1.159290225047545e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.897279007717995e-09</v>
+        <v>8.897279007717944e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>8.086585950472293e-09</v>
+        <v>8.086585950472288e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.965134919662541e-09</v>
+        <v>4.965134919662528e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.724417147525632e-09</v>
+        <v>3.724417147525525e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.811875147753494e-09</v>
+        <v>8.811875147753454e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>5.674233880633257e-09</v>
+        <v>5.6742338806332e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>6.3315599841944e-09</v>
+        <v>6.331559984194368e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.211879225595347e-09</v>
+        <v>4.211879225595306e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.007595834488684e-09</v>
+        <v>3.007595834488625e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.58731041928158e-09</v>
+        <v>4.587310419281562e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.415279686438389e-08</v>
+        <v>1.415279686438385e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>4.431374110544926e-09</v>
+        <v>4.431374110544866e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>6.269409905605225e-09</v>
+        <v>6.269409905605168e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.388447101783048e-09</v>
+        <v>7.388447101782997e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>7.221286711554598e-09</v>
+        <v>7.221286711554555e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>6.283259177542819e-09</v>
+        <v>6.283259177542756e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.89389995572456e-09</v>
+        <v>4.893899955724521e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>6.407379633517957e-09</v>
+        <v>6.407379633517908e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.988617251894581e-09</v>
+        <v>5.988617251894593e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.835602439521218e-08</v>
+        <v>2.835602439521211e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.116931751180879e-09</v>
+        <v>7.116931751180814e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.741412535450471e-09</v>
+        <v>6.741412535450414e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.884843636477966e-09</v>
+        <v>5.884843636477908e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.652443120290954e-09</v>
+        <v>5.652443120290906e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.251805593812778e-09</v>
+        <v>4.251805593812776e-09</v>
       </c>
     </row>
     <row r="7">
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.761540960578683e-09</v>
+        <v>2.761540960578639e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>3.065008677897897e-09</v>
+        <v>3.065008677897895e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.987759769671226e-09</v>
+        <v>2.98775976967124e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.821303578737841e-09</v>
+        <v>2.821303578737829e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.764599352635406e-09</v>
+        <v>2.764599352635397e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.937743875522359e-09</v>
+        <v>2.937743875522441e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.987759769671226e-09</v>
+        <v>2.98775976967124e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.987759769671226e-09</v>
+        <v>2.98775976967124e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.863417489564963e-09</v>
+        <v>2.863417489564842e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.987759769671226e-09</v>
+        <v>2.987759769671243e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.987759769671226e-09</v>
+        <v>2.98775976967124e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.93514873162962e-09</v>
+        <v>2.935148731629603e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.812402346859793e-09</v>
+        <v>2.812402346859676e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.763668251051443e-09</v>
+        <v>2.763668251051384e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.751855780889338e-09</v>
+        <v>2.75185578088926e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.717083801584025e-09</v>
+        <v>2.717083801584092e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.987759769671226e-09</v>
+        <v>2.98775976967124e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.987759769671226e-09</v>
+        <v>2.987759769671243e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.987759769671226e-09</v>
+        <v>2.987759769671243e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.779050748476366e-09</v>
+        <v>2.779050748476422e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.760067177892949e-09</v>
+        <v>2.760067177892934e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.890880389611286e-09</v>
+        <v>2.89088038961129e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.640893366673998e-09</v>
+        <v>2.64089336667388e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.21033893970598e-09</v>
+        <v>3.210338939706071e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.757338830116943e-09</v>
+        <v>2.757338830116844e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.987759769671226e-09</v>
+        <v>2.98775976967124e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.194220834117577e-09</v>
+        <v>3.194220834117571e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>6.774908250922976e-09</v>
+        <v>6.774908250922949e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.695965333336472e-09</v>
+        <v>6.695965333336449e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.131582665931773e-09</v>
+        <v>8.131582665931758e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>3.205580517703632e-08</v>
+        <v>3.20558051770363e-08</v>
       </c>
       <c r="D9" t="n">
         <v>2.433546119154051e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.208074804441309e-08</v>
+        <v>2.208074804441308e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.28363282615476e-08</v>
+        <v>1.283632826154757e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.368927543230452e-09</v>
+        <v>9.368927543230566e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>2.408364571660271e-08</v>
+        <v>2.408364571660269e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.483222984157066e-08</v>
+        <v>1.483222984157065e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.713699915011235e-08</v>
+        <v>1.713699915011234e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.052043957659833e-08</v>
+        <v>1.05204395765983e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.969579062595967e-09</v>
+        <v>6.969579062595927e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.178253309229264e-08</v>
+        <v>1.17825330922926e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.983149059432121e-08</v>
+        <v>3.983149059432114e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>1.145340830882312e-08</v>
+        <v>1.14534083088231e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>1.687290406555275e-08</v>
+        <v>1.687290406555268e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.988663155840251e-08</v>
+        <v>1.988663155840246e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>1.939375485384051e-08</v>
+        <v>1.939375485384048e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.662795657399486e-08</v>
+        <v>1.662795657399483e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.253139521895876e-08</v>
+        <v>1.253139521895868e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.727971135243456e-08</v>
+        <v>1.727971135243457e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.62437922783399e-08</v>
+        <v>1.624379227833991e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.199585424347398e-08</v>
+        <v>8.199585424347384e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.937184399815738e-08</v>
+        <v>1.937184399815734e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.797883351871212e-08</v>
+        <v>1.797883351871211e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.545321811676846e-08</v>
+        <v>1.545321811676843e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.476797922494594e-08</v>
+        <v>1.476797922494589e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.072615752190852e-08</v>
+        <v>1.07261575219085e-08</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.244079946277562e-09</v>
+        <v>6.244079946277539e-09</v>
       </c>
       <c r="C10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="D10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="E10" t="n">
-        <v>6.555927718124508e-09</v>
+        <v>6.555927718124478e-09</v>
       </c>
       <c r="F10" t="n">
-        <v>6.347992615372152e-09</v>
+        <v>6.34799261537213e-09</v>
       </c>
       <c r="G10" t="n">
-        <v>7.049401192867165e-09</v>
+        <v>7.049401192867132e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="M10" t="n">
-        <v>6.911091915943146e-09</v>
+        <v>6.911091915943108e-09</v>
       </c>
       <c r="N10" t="n">
-        <v>6.394046050241652e-09</v>
+        <v>6.394046050241632e-09</v>
       </c>
       <c r="O10" t="n">
-        <v>6.536134742504159e-09</v>
+        <v>6.536134742504123e-09</v>
       </c>
       <c r="P10" t="n">
-        <v>6.50130537079538e-09</v>
+        <v>6.501305370795357e-09</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.112996870977931e-09</v>
+        <v>6.112996870977907e-09</v>
       </c>
       <c r="R10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="S10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="T10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="U10" t="n">
-        <v>6.581490431303486e-09</v>
+        <v>6.581490431303466e-09</v>
       </c>
       <c r="V10" t="n">
-        <v>6.72432945097591e-09</v>
+        <v>6.724329450975884e-09</v>
       </c>
       <c r="W10" t="n">
-        <v>6.911223000840904e-09</v>
+        <v>6.911223000840877e-09</v>
       </c>
       <c r="X10" t="n">
-        <v>6.174129842107129e-09</v>
+        <v>6.174129842107105e-09</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.567372316342697e-09</v>
+        <v>7.567372316342661e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.231689856667818e-09</v>
+        <v>6.231689856667792e-09</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.911091915938126e-09</v>
+        <v>6.911091915938098e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.607841690979877e-09</v>
+        <v>7.607841690979832e-09</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="C11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="E11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="I11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="J11" t="n">
-        <v>5.997394697192004e-08</v>
+        <v>5.997394697191986e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="L11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="M11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="N11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="R11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="S11" t="n">
-        <v>5.747846052813023e-08</v>
+        <v>5.74784605281302e-08</v>
       </c>
       <c r="T11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="U11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="V11" t="n">
-        <v>7.4347809045325e-08</v>
+        <v>7.434780904532479e-08</v>
       </c>
       <c r="W11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="X11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.743965807632912e-08</v>
+        <v>5.743965807632893e-08</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.814530050830297e-08</v>
+        <v>5.814530050830291e-08</v>
       </c>
       <c r="C12" t="n">
-        <v>6.990466435305352e-08</v>
+        <v>6.990466435305347e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>6.610991892757779e-08</v>
+        <v>6.610991892757775e-08</v>
       </c>
       <c r="E12" t="n">
-        <v>6.500167007015697e-08</v>
+        <v>6.500167007015682e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>6.045780262744821e-08</v>
+        <v>6.045780262744823e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>5.875348698570429e-08</v>
+        <v>5.875348698570428e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>6.598614521705675e-08</v>
+        <v>6.598614521705658e-08</v>
       </c>
       <c r="I12" t="n">
-        <v>6.143883901711195e-08</v>
+        <v>6.143883901711188e-08</v>
       </c>
       <c r="J12" t="n">
-        <v>6.510598064657011e-08</v>
+        <v>6.510598064657003e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>5.931948443727018e-08</v>
+        <v>5.931948443727012e-08</v>
       </c>
       <c r="L12" t="n">
-        <v>5.757414618325873e-08</v>
+        <v>5.757414618325867e-08</v>
       </c>
       <c r="M12" t="n">
-        <v>5.993983549989136e-08</v>
+        <v>5.993983549989121e-08</v>
       </c>
       <c r="N12" t="n">
-        <v>7.372661149978875e-08</v>
+        <v>7.372661149978867e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>5.977806229796825e-08</v>
+        <v>5.977806229796819e-08</v>
       </c>
       <c r="P12" t="n">
-        <v>6.244188230001372e-08</v>
+        <v>6.244188230001358e-08</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.392320601286982e-08</v>
+        <v>6.392320601286985e-08</v>
       </c>
       <c r="R12" t="n">
-        <v>6.368094457691912e-08</v>
+        <v>6.368094457691905e-08</v>
       </c>
       <c r="S12" t="n">
-        <v>6.232148437800178e-08</v>
+        <v>6.232148437800168e-08</v>
       </c>
       <c r="T12" t="n">
-        <v>6.030792028145257e-08</v>
+        <v>6.03079202814524e-08</v>
       </c>
       <c r="U12" t="n">
-        <v>6.264183842811431e-08</v>
+        <v>6.264183842811429e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>7.904080882497909e-08</v>
+        <v>7.904080882497914e-08</v>
       </c>
       <c r="W12" t="n">
-        <v>9.44514686274394e-08</v>
+        <v>9.445146862743925e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>6.36701748340776e-08</v>
+        <v>6.367017483407751e-08</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.298547475407521e-08</v>
+        <v>6.298547475407519e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.174407054837637e-08</v>
+        <v>6.174407054837631e-08</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.140725820491258e-08</v>
+        <v>6.140725820491251e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.942060003955047e-08</v>
+        <v>5.942060003955034e-08</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.721754491549033e-08</v>
+        <v>5.721754491549019e-08</v>
       </c>
       <c r="C13" t="n">
-        <v>5.754539826313424e-08</v>
+        <v>5.7545398263134e-08</v>
       </c>
       <c r="D13" t="n">
-        <v>5.754539826313424e-08</v>
+        <v>5.7545398263134e-08</v>
       </c>
       <c r="E13" t="n">
-        <v>5.737082602678338e-08</v>
+        <v>5.737082602678332e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>5.726862063522979e-08</v>
+        <v>5.72686206352298e-08</v>
       </c>
       <c r="G13" t="n">
-        <v>5.761338079045595e-08</v>
+        <v>5.761338079045583e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>5.754539826313424e-08</v>
+        <v>5.7545398263134e-08</v>
       </c>
       <c r="I13" t="n">
-        <v>5.754539826313424e-08</v>
+        <v>5.7545398263134e-08</v>
       </c>
       <c r="J13" t="n">
-        <v>6.007968715872513e-08</v>
+        <v>6.007968715872504e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>5.754539826313424e-08</v>
+        <v>5.7545398263134e-08</v>
       </c>
       <c r="L13" t="n">
-        <v>5.754539826313424e-08</v>
+        <v>5.7545398263134e-08</v>
       </c>
       <c r="M13" t="n">
-        <v>5.754539826313669e-08</v>
+        <v>5.754539826313649e-08</v>
       </c>
       <c r="N13" t="n">
-        <v>5.729125706977556e-08</v>
+        <v>5.729125706977545e-08</v>
       </c>
       <c r="O13" t="n">
-        <v>5.736109727585814e-08</v>
+        <v>5.736109727585806e-08</v>
       </c>
       <c r="P13" t="n">
-        <v>5.734397775382485e-08</v>
+        <v>5.734397775382474e-08</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.715311425005815e-08</v>
+        <v>5.715311425005817e-08</v>
       </c>
       <c r="R13" t="n">
-        <v>5.754539826313424e-08</v>
+        <v>5.7545398263134e-08</v>
       </c>
       <c r="S13" t="n">
-        <v>5.754539826313424e-08</v>
+        <v>5.7545398263134e-08</v>
       </c>
       <c r="T13" t="n">
-        <v>5.754539826313424e-08</v>
+        <v>5.7545398263134e-08</v>
       </c>
       <c r="U13" t="n">
         <v>5.738339075046413e-08</v>
       </c>
       <c r="V13" t="n">
-        <v>7.436175073054806e-08</v>
+        <v>7.436175073054795e-08</v>
       </c>
       <c r="W13" t="n">
-        <v>5.75454626946979e-08</v>
+        <v>5.754546269469778e-08</v>
       </c>
       <c r="X13" t="n">
-        <v>5.718316266020345e-08</v>
+        <v>5.718316266020334e-08</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.786797677154561e-08</v>
+        <v>5.786797677154565e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.721145487132178e-08</v>
+        <v>5.721145487132169e-08</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.754539826313424e-08</v>
+        <v>5.7545398263134e-08</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.788786849846414e-08</v>
+        <v>5.788786849846417e-08</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="C14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="D14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="F14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>5.932411560367991e-09</v>
+        <v>5.932411560367971e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>5.935637503970693e-09</v>
+        <v>5.935637503970668e-09</v>
       </c>
       <c r="K14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="L14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="M14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="N14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="O14" t="n">
-        <v>5.932411560367991e-09</v>
+        <v>5.932411560367971e-09</v>
       </c>
       <c r="P14" t="n">
-        <v>5.932411560367991e-09</v>
+        <v>5.932411560367971e-09</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="R14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="S14" t="n">
-        <v>6.0545561644122e-09</v>
+        <v>6.05455616441218e-09</v>
       </c>
       <c r="T14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="U14" t="n">
-        <v>5.932411560367991e-09</v>
+        <v>5.932411560367973e-09</v>
       </c>
       <c r="V14" t="n">
-        <v>5.93727423679985e-09</v>
+        <v>5.937274236799822e-09</v>
       </c>
       <c r="W14" t="n">
-        <v>5.932411560367991e-09</v>
+        <v>5.932411560367971e-09</v>
       </c>
       <c r="X14" t="n">
-        <v>5.932411560367991e-09</v>
+        <v>5.932411560367971e-09</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.015753712611105e-09</v>
+        <v>6.01575371261109e-09</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.721396144584921e-09</v>
+        <v>6.721396144584901e-09</v>
       </c>
       <c r="C15" t="n">
-        <v>1.848075998933552e-08</v>
+        <v>1.848075998933551e-08</v>
       </c>
       <c r="D15" t="n">
-        <v>1.468601456385982e-08</v>
+        <v>1.468601456385979e-08</v>
       </c>
       <c r="E15" t="n">
-        <v>1.357776570643895e-08</v>
+        <v>1.357776570643894e-08</v>
       </c>
       <c r="F15" t="n">
-        <v>9.033898263730283e-09</v>
+        <v>9.033898263730258e-09</v>
       </c>
       <c r="G15" t="n">
-        <v>7.246240469743212e-09</v>
+        <v>7.246240469743147e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>1.456224085333868e-08</v>
+        <v>1.456224085333867e-08</v>
       </c>
       <c r="I15" t="n">
-        <v>1.001493465339393e-08</v>
+        <v>1.00149346533939e-08</v>
       </c>
       <c r="J15" t="n">
-        <v>1.106767117862091e-08</v>
+        <v>1.106767117862086e-08</v>
       </c>
       <c r="K15" t="n">
-        <v>7.895580073552147e-09</v>
+        <v>7.895580073552128e-09</v>
       </c>
       <c r="L15" t="n">
-        <v>6.15024181954072e-09</v>
+        <v>6.150241819540701e-09</v>
       </c>
       <c r="M15" t="n">
-        <v>8.515931136173357e-09</v>
+        <v>8.515931136173329e-09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.230270713607074e-08</v>
+        <v>2.230270713607068e-08</v>
       </c>
       <c r="O15" t="n">
-        <v>8.270815782007105e-09</v>
+        <v>8.270815782007097e-09</v>
       </c>
       <c r="P15" t="n">
-        <v>1.093463578405253e-08</v>
+        <v>1.093463578405251e-08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.24993016491519e-08</v>
+        <v>1.249930164915187e-08</v>
       </c>
       <c r="R15" t="n">
-        <v>1.225704021320112e-08</v>
+        <v>1.225704021320108e-08</v>
       </c>
       <c r="S15" t="n">
-        <v>1.089758001428372e-08</v>
+        <v>1.089758001428369e-08</v>
       </c>
       <c r="T15" t="n">
-        <v>8.88401591773452e-09</v>
+        <v>8.88401591773448e-09</v>
       </c>
       <c r="U15" t="n">
-        <v>1.113459191215319e-08</v>
+        <v>1.113459191215313e-08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.063027401645394e-08</v>
+        <v>1.063027401645391e-08</v>
       </c>
       <c r="W15" t="n">
-        <v>4.294422211147821e-08</v>
+        <v>4.294422211147823e-08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.216292831811649e-08</v>
+        <v>1.216292831811646e-08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.156157039035725e-08</v>
+        <v>1.156157039035724e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.032016618465834e-08</v>
+        <v>1.032016618465832e-08</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.98335384119454e-09</v>
+        <v>9.98335384119451e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.996695675832399e-09</v>
+        <v>7.996695675832379e-09</v>
       </c>
     </row>
     <row r="16">
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.793640551772325e-09</v>
+        <v>5.793640551772309e-09</v>
       </c>
       <c r="C16" t="n">
-        <v>6.121493899416193e-09</v>
+        <v>6.121493899416165e-09</v>
       </c>
       <c r="D16" t="n">
-        <v>6.121493899416193e-09</v>
+        <v>6.121493899416165e-09</v>
       </c>
       <c r="E16" t="n">
-        <v>5.946921663065322e-09</v>
+        <v>5.9469216630653e-09</v>
       </c>
       <c r="F16" t="n">
-        <v>5.84471627151182e-09</v>
+        <v>5.844716271511796e-09</v>
       </c>
       <c r="G16" t="n">
-        <v>6.106134274494835e-09</v>
+        <v>6.10613427449481e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>6.121493899416193e-09</v>
+        <v>6.121493899416165e-09</v>
       </c>
       <c r="I16" t="n">
-        <v>6.121493899416193e-09</v>
+        <v>6.121493899416165e-09</v>
       </c>
       <c r="J16" t="n">
-        <v>6.04137769077578e-09</v>
+        <v>6.041377690775751e-09</v>
       </c>
       <c r="K16" t="n">
-        <v>6.121493899416193e-09</v>
+        <v>6.121493899416165e-09</v>
       </c>
       <c r="L16" t="n">
-        <v>6.121493899416193e-09</v>
+        <v>6.121493899416165e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>6.121493899418658e-09</v>
+        <v>6.121493899418635e-09</v>
       </c>
       <c r="N16" t="n">
-        <v>5.867352706057588e-09</v>
+        <v>5.86735270605757e-09</v>
       </c>
       <c r="O16" t="n">
-        <v>5.85385075989699e-09</v>
+        <v>5.853850759896968e-09</v>
       </c>
       <c r="P16" t="n">
-        <v>5.836731237863728e-09</v>
+        <v>5.836731237863704e-09</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.729209886340181e-09</v>
+        <v>5.729209886340158e-09</v>
       </c>
       <c r="R16" t="n">
-        <v>6.121493899416193e-09</v>
+        <v>6.121493899416165e-09</v>
       </c>
       <c r="S16" t="n">
-        <v>6.121493899416193e-09</v>
+        <v>6.121493899416165e-09</v>
       </c>
       <c r="T16" t="n">
-        <v>6.121493899416193e-09</v>
+        <v>6.121493899416165e-09</v>
       </c>
       <c r="U16" t="n">
-        <v>5.876144234503034e-09</v>
+        <v>5.876144234503012e-09</v>
       </c>
       <c r="V16" t="n">
-        <v>5.951215922022959e-09</v>
+        <v>5.951215922022934e-09</v>
       </c>
       <c r="W16" t="n">
-        <v>6.038216178736763e-09</v>
+        <v>6.03821617873674e-09</v>
       </c>
       <c r="X16" t="n">
-        <v>5.675916144242273e-09</v>
+        <v>5.675916144242248e-09</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.444072407827653e-09</v>
+        <v>6.444072407827629e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.787550507603812e-09</v>
+        <v>5.787550507603788e-09</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.121493899416193e-09</v>
+        <v>6.121493899416165e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.463964134746139e-09</v>
+        <v>6.463964134746111e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.871819065707098e-09</v>
+        <v>5.871819065707084e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>2.980909315611521e-08</v>
+        <v>2.980909315611523e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>8.186548568279123e-09</v>
+        <v>8.186548568278981e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>1.188550680838824e-08</v>
+        <v>1.188550680838827e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.131072064724182e-08</v>
+        <v>1.131072064724175e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.130185010439602e-09</v>
+        <v>7.130185010439306e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.844987753356049e-08</v>
+        <v>1.844987753356052e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.194032650416941e-09</v>
+        <v>7.194032650416893e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.26730375767412e-08</v>
+        <v>1.267303757674109e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>5.710845498353896e-09</v>
+        <v>5.710845498353883e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>6.59206327763623e-09</v>
+        <v>6.592063277636119e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>8.312994134939262e-09</v>
+        <v>8.312994134939242e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.615119801097552e-08</v>
+        <v>2.615119801097556e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>6.363102830433521e-09</v>
+        <v>6.363102830433464e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.263668355418891e-08</v>
+        <v>1.263668355418903e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.478170358368185e-08</v>
+        <v>1.478170358368186e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.420867522153738e-08</v>
+        <v>1.420867522153737e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.235155522692333e-08</v>
+        <v>1.235155522692339e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>9.37178149444791e-09</v>
+        <v>9.37178149444789e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.847593878248046e-08</v>
+        <v>1.847593878248042e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36610816072484e-08</v>
+        <v>1.366108160724829e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.776150426760056e-08</v>
+        <v>6.77615042676006e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.225916339198708e-08</v>
+        <v>1.225916339198705e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.052215960434401e-08</v>
+        <v>1.052215960434389e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.224658641698718e-09</v>
+        <v>9.224658641698689e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.31525017554581e-08</v>
+        <v>1.315250175545806e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.561877635736311e-09</v>
+        <v>6.561877635736319e-09</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.13601487853451e-09</v>
+        <v>3.136014878534443e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>3.802478011246249e-09</v>
+        <v>3.802478011246281e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>3.71180166290176e-09</v>
+        <v>3.711801662901761e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.358597107528721e-09</v>
+        <v>3.358597107528746e-09</v>
       </c>
       <c r="F3" t="n">
         <v>3.209783337541623e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>3.831194803415608e-09</v>
+        <v>3.831194803415645e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>3.71180166290176e-09</v>
+        <v>3.711801662901761e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.71180166290176e-09</v>
+        <v>3.711801662901761e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.686265043761888e-09</v>
+        <v>3.686265043761956e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.71180166290176e-09</v>
+        <v>3.711801662901761e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>3.71180166290176e-09</v>
+        <v>3.711801662901761e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.668708493174148e-09</v>
+        <v>3.668708493174155e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.26547057755714e-09</v>
+        <v>3.265470577557022e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.388126234389032e-09</v>
+        <v>3.388126234389029e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.358060369208265e-09</v>
+        <v>3.358060369208275e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.02285963414353e-09</v>
+        <v>3.022859634143596e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>3.71180166290176e-09</v>
+        <v>3.711801662901761e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>3.71180166290176e-09</v>
+        <v>3.711801662901761e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>3.71180166290176e-09</v>
+        <v>3.711801662901761e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.417950556331796e-09</v>
+        <v>3.417950556331872e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.479316415295139e-09</v>
+        <v>3.479316415295103e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.711914819860543e-09</v>
+        <v>3.71191481986055e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.075631636030638e-09</v>
+        <v>3.075631636030575e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.26236675184009e-09</v>
+        <v>4.262366751840119e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.125319343538895e-09</v>
+        <v>3.12531934353896e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.71180166290176e-09</v>
+        <v>3.711801662901761e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.289691922363113e-09</v>
+        <v>4.289691922363151e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.329186140722191e-08</v>
+        <v>6.329186140722213e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.207434261166029e-08</v>
+        <v>7.207434261166037e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.413555312998333e-08</v>
+        <v>6.413555312998329e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.545415554390163e-08</v>
+        <v>6.545415554390171e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.52641519444024e-08</v>
+        <v>6.526415194440242e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.375052101759791e-08</v>
+        <v>6.375052101759782e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.787641601973499e-08</v>
+        <v>6.787641601973507e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.377379273263289e-08</v>
+        <v>6.377379273263298e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.870034719784063e-08</v>
+        <v>6.870034719784071e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.323318843216874e-08</v>
+        <v>6.32331884321688e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.355438196493561e-08</v>
+        <v>6.35543819649356e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.415425483884162e-08</v>
+        <v>6.415425483884173e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.06834569002819e-08</v>
+        <v>7.068345690028198e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.347092857051953e-08</v>
+        <v>6.347092857051949e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.575757507622409e-08</v>
+        <v>6.575757507622398e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.653940968887747e-08</v>
+        <v>6.653940968887739e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.633054757971454e-08</v>
+        <v>6.633054757971455e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.565364914908166e-08</v>
+        <v>6.565364914908175e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.456755661386417e-08</v>
+        <v>6.45675566138641e-08</v>
       </c>
       <c r="U4" t="n">
         <v>6.788591503893965e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.57455150633899e-08</v>
+        <v>8.574551506338999e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>8.584992491793665e-08</v>
+        <v>8.584992491793684e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.561997341016712e-08</v>
+        <v>6.561997341016708e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.498685592649949e-08</v>
+        <v>6.498685592649941e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.451393206164083e-08</v>
+        <v>6.451393206164073e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.594558475354358e-08</v>
+        <v>6.594558475354372e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.352840243214091e-08</v>
+        <v>6.352840243214095e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6757,82 +6757,82 @@
         <v>6.22946929064322e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.259523677644884e-08</v>
+        <v>6.259523677644888e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.250456042810436e-08</v>
+        <v>6.250456042810446e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.23461970859673e-08</v>
+        <v>6.234619708596738e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.231145542102523e-08</v>
+        <v>6.231145542102535e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.254807782583656e-08</v>
+        <v>6.254807782583674e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.250456042810436e-08</v>
+        <v>6.250456042810446e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.250456042810436e-08</v>
+        <v>6.250456042810446e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.542477413758062e-08</v>
+        <v>6.542477413758074e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.250456042810436e-08</v>
+        <v>6.250456042810446e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.250456042810436e-08</v>
+        <v>6.250456042810446e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.246146725837363e-08</v>
+        <v>6.246146725837376e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.234187798858046e-08</v>
+        <v>6.234187798858041e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.238658453520022e-08</v>
+        <v>6.23865845352002e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.237562588039305e-08</v>
+        <v>6.237562588039313e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.225344914858769e-08</v>
+        <v>6.225344914858779e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.250456042810436e-08</v>
+        <v>6.250456042810446e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.250456042810436e-08</v>
+        <v>6.250456042810446e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.250456042810436e-08</v>
+        <v>6.250456042810446e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.239745515033348e-08</v>
+        <v>6.239745515033359e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.203438121124607e-08</v>
+        <v>8.203438121124626e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.250460167248704e-08</v>
+        <v>6.250460167248726e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.227268392359544e-08</v>
+        <v>6.227268392359536e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.270523493796063e-08</v>
+        <v>6.27052349379608e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.229079450951972e-08</v>
+        <v>6.229079450951956e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.250456042810436e-08</v>
+        <v>6.250456042810446e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.270021742096817e-08</v>
+        <v>6.27002174209681e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.649912343605577e-09</v>
+        <v>3.649912343605578e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.243239354804391e-08</v>
+        <v>1.243239354804392e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.493604066366954e-09</v>
+        <v>4.493604066366903e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>5.812206480285266e-09</v>
+        <v>5.812206480285302e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.622202880786031e-09</v>
+        <v>5.622202880786016e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.015944465060392e-09</v>
+        <v>4.015944465060263e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.234466956118604e-09</v>
+        <v>8.234466956118624e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.131843669016517e-09</v>
+        <v>4.131843669016453e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>6.023518465155138e-09</v>
+        <v>6.023518465155163e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>3.591239368552384e-09</v>
+        <v>3.591239368552405e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.912432901319187e-09</v>
+        <v>3.912432901319118e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.512305775225263e-09</v>
+        <v>4.512305775225238e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.104150783666555e-08</v>
+        <v>1.104150783666552e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.736352017981948e-09</v>
+        <v>3.736352017981933e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>6.022998523686578e-09</v>
+        <v>6.022998523686494e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.897460625261064e-09</v>
+        <v>6.897460625260991e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>6.688598516098154e-09</v>
+        <v>6.688598516098077e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>6.011700085465326e-09</v>
+        <v>6.011700085465269e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.92560755024778e-09</v>
+        <v>4.925607550247758e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>8.151338486402109e-09</v>
+        <v>8.151338486402041e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>6.362813817603637e-09</v>
+        <v>6.362813817603597e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.611534836539912e-08</v>
+        <v>2.611534836539924e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.885396857629579e-09</v>
+        <v>5.885396857629475e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.344906862883136e-09</v>
+        <v>5.344906862883019e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.871982998024463e-09</v>
+        <v>4.871982998024386e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.303635689927261e-09</v>
+        <v>6.303635689927325e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.886453368524568e-09</v>
+        <v>3.886453368524549e-09</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.652743842815878e-09</v>
+        <v>2.652743842815926e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.953287712832447e-09</v>
+        <v>2.95328771283247e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.862611364487958e-09</v>
+        <v>2.862611364488017e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.704248022350921e-09</v>
+        <v>2.704248022350931e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.669506357408911e-09</v>
+        <v>2.669506357408926e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.813501273299028e-09</v>
+        <v>2.813501273299048e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.862611364487958e-09</v>
+        <v>2.862611364488017e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.862611364487958e-09</v>
+        <v>2.862611364488017e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.747945404895154e-09</v>
+        <v>2.74794540489517e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.862611364487958e-09</v>
+        <v>2.862611364488017e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.862611364487958e-09</v>
+        <v>2.862611364488017e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.81951819475729e-09</v>
+        <v>2.819518194757281e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.699928924964058e-09</v>
+        <v>2.699928924963952e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.652007982662659e-09</v>
+        <v>2.65200798266259e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.641049327855482e-09</v>
+        <v>2.641049327855465e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.611500084971329e-09</v>
+        <v>2.611500084971321e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.862611364487958e-09</v>
+        <v>2.862611364488017e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.862611364487958e-09</v>
+        <v>2.862611364488017e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.862611364487958e-09</v>
+        <v>2.862611364488017e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.662878597795919e-09</v>
+        <v>2.662878597795898e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.651679965459932e-09</v>
+        <v>2.651679965459942e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.770025119949493e-09</v>
+        <v>2.770025119949566e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.538107371057861e-09</v>
+        <v>2.538107371057774e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.06328587434429e-09</v>
+        <v>3.063285874344314e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.648845445903288e-09</v>
+        <v>2.648845445903188e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.862611364487958e-09</v>
+        <v>2.862611364488017e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.058268357351768e-09</v>
+        <v>3.058268357351783e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260007e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>6.619727551476288e-09</v>
+        <v>6.619727551476291e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.537129911260012e-09</v>
+        <v>6.537129911260004e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.052947529922736e-09</v>
+        <v>9.052947529922739e-09</v>
       </c>
       <c r="C9" t="n">
         <v>3.468095742097994e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.154059424702227e-08</v>
+        <v>1.154059424702222e-08</v>
       </c>
       <c r="E9" t="n">
         <v>1.556597309032739e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.491527391086649e-08</v>
+        <v>1.491527391086639e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.040531717304739e-08</v>
+        <v>1.04053171730472e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.257062457178603e-08</v>
+        <v>2.257062457178604e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.047393442262576e-08</v>
+        <v>1.047393442262575e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.638968167926907e-08</v>
+        <v>1.638968167926902e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.879948755802024e-09</v>
+        <v>8.879948755801997e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>9.826996137902398e-09</v>
+        <v>9.826996137902362e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.17227980339181e-08</v>
+        <v>1.172279803391805e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.084725671462832e-08</v>
+        <v>3.084725671462836e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>9.580931660737165e-09</v>
+        <v>9.580931660737162e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.632316762159902e-08</v>
+        <v>1.632316762159916e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.862842706057523e-08</v>
+        <v>1.862842706057524e-08</v>
       </c>
       <c r="R9" t="n">
         <v>1.801259176651185e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.601673935579685e-08</v>
+        <v>1.601673935579681e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.28143676164401e-08</v>
+        <v>1.281436761644011e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>2.259863267391944e-08</v>
+        <v>2.259863267391937e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.748962340699134e-08</v>
+        <v>1.748962340699136e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.556597725704254e-08</v>
+        <v>7.556597725704243e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.591744557455348e-08</v>
+        <v>1.591744557455346e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.405068241059917e-08</v>
+        <v>1.405068241059897e-08</v>
       </c>
       <c r="Z9" t="n">
         <v>1.265625424671585e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.687751898472016e-08</v>
+        <v>1.687751898472015e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.819883259055197e-09</v>
+        <v>9.819883259055184e-09</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.112770590334393e-09</v>
+        <v>6.112770590334392e-09</v>
       </c>
       <c r="C10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="D10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="E10" t="n">
-        <v>6.40207774066446e-09</v>
+        <v>6.402077740664462e-09</v>
       </c>
       <c r="F10" t="n">
-        <v>6.209172363574439e-09</v>
+        <v>6.20917236357444e-09</v>
       </c>
       <c r="G10" t="n">
         <v>6.859882534085218e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="M10" t="n">
-        <v>6.731570369013016e-09</v>
+        <v>6.731570369013022e-09</v>
       </c>
       <c r="N10" t="n">
         <v>6.251897017126658e-09</v>
       </c>
       <c r="O10" t="n">
-        <v>6.383715418245448e-09</v>
+        <v>6.38371541824545e-09</v>
       </c>
       <c r="P10" t="n">
-        <v>6.35140354304336e-09</v>
+        <v>6.351403543043359e-09</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.991162310870623e-09</v>
+        <v>5.991162310870627e-09</v>
       </c>
       <c r="R10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="S10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="T10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="U10" t="n">
         <v>6.415767706207479e-09</v>
       </c>
       <c r="V10" t="n">
-        <v>6.547249913286513e-09</v>
+        <v>6.547249913286508e-09</v>
       </c>
       <c r="W10" t="n">
-        <v>6.73169197912978e-09</v>
+        <v>6.731691979129783e-09</v>
       </c>
       <c r="X10" t="n">
-        <v>6.047876539078875e-09</v>
+        <v>6.047876539078874e-09</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.32326431619485e-09</v>
+        <v>7.323264316194847e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.101276066896607e-09</v>
+        <v>6.101276066896611e-09</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.731570369007853e-09</v>
+        <v>6.731570369007856e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.377958479407024e-09</v>
+        <v>7.377958479407026e-09</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="C11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="E11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="I11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="J11" t="n">
         <v>5.972324888925989e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="L11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188753e-08</v>
       </c>
       <c r="M11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="N11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="R11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="S11" t="n">
-        <v>5.723087899281412e-08</v>
+        <v>5.723087899281419e-08</v>
       </c>
       <c r="T11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="U11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="V11" t="n">
-        <v>7.408962331633003e-08</v>
+        <v>7.40896233163302e-08</v>
       </c>
       <c r="W11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="X11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.719028015188752e-08</v>
+        <v>5.719028015188755e-08</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.842686849791039e-08</v>
+        <v>5.842686849791035e-08</v>
       </c>
       <c r="C12" t="n">
-        <v>7.102368717345675e-08</v>
+        <v>7.102368717345677e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>5.964961012932574e-08</v>
+        <v>5.964961012932587e-08</v>
       </c>
       <c r="E12" t="n">
-        <v>6.162818621092739e-08</v>
+        <v>6.162818621092743e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>6.130835101456056e-08</v>
+        <v>6.130835101456061e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>5.909159257321593e-08</v>
+        <v>5.909159257321586e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>6.507115056798896e-08</v>
+        <v>6.507115056798902e-08</v>
       </c>
       <c r="I12" t="n">
         <v>5.912531969657147e-08</v>
       </c>
       <c r="J12" t="n">
-        <v>6.456602866968877e-08</v>
+        <v>6.456602866968875e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>5.834183520043798e-08</v>
+        <v>5.834183520043811e-08</v>
       </c>
       <c r="L12" t="n">
-        <v>5.88073330756215e-08</v>
+        <v>5.880733307562161e-08</v>
       </c>
       <c r="M12" t="n">
         <v>5.973916792469422e-08</v>
       </c>
       <c r="N12" t="n">
-        <v>6.913932577124431e-08</v>
+        <v>6.913932577124439e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>5.868638612677452e-08</v>
+        <v>5.868638612677458e-08</v>
       </c>
       <c r="P12" t="n">
-        <v>6.200036658127568e-08</v>
+        <v>6.200036658127575e-08</v>
       </c>
       <c r="Q12" t="n">
         <v>6.313346022671742e-08</v>
       </c>
       <c r="R12" t="n">
-        <v>6.283076151673974e-08</v>
+        <v>6.283076151673971e-08</v>
       </c>
       <c r="S12" t="n">
-        <v>6.184974929504159e-08</v>
+        <v>6.184974929504164e-08</v>
       </c>
       <c r="T12" t="n">
-        <v>6.027570213711352e-08</v>
+        <v>6.027570213711356e-08</v>
       </c>
       <c r="U12" t="n">
-        <v>6.508491726253608e-08</v>
+        <v>6.50849172625361e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>7.947305243147882e-08</v>
+        <v>7.947305243147872e-08</v>
       </c>
       <c r="W12" t="n">
-        <v>9.111971427857791e-08</v>
+        <v>9.111971427857779e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>6.180094387615617e-08</v>
+        <v>6.180094387615614e-08</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.088338230245289e-08</v>
+        <v>6.088338230245287e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.019798539449235e-08</v>
+        <v>6.019798539449237e-08</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.227284437543384e-08</v>
+        <v>6.227284437543401e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.880383691476163e-08</v>
+        <v>5.880383691476159e-08</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.698169675264186e-08</v>
+        <v>5.698169675264182e-08</v>
       </c>
       <c r="C13" t="n">
-        <v>5.728585258220308e-08</v>
+        <v>5.728585258220317e-08</v>
       </c>
       <c r="D13" t="n">
-        <v>5.728585258220308e-08</v>
+        <v>5.728585258220317e-08</v>
       </c>
       <c r="E13" t="n">
-        <v>5.712389857516879e-08</v>
+        <v>5.712389857516886e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>5.70290806760393e-08</v>
+        <v>5.702908067603927e-08</v>
       </c>
       <c r="G13" t="n">
-        <v>5.73489212747866e-08</v>
+        <v>5.734892127478666e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>5.728585258220308e-08</v>
+        <v>5.728585258220317e-08</v>
       </c>
       <c r="I13" t="n">
-        <v>5.728585258220308e-08</v>
+        <v>5.728585258220317e-08</v>
       </c>
       <c r="J13" t="n">
-        <v>5.981882131957547e-08</v>
+        <v>5.981882131957551e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>5.728585258220308e-08</v>
+        <v>5.728585258220317e-08</v>
       </c>
       <c r="L13" t="n">
-        <v>5.728585258220308e-08</v>
+        <v>5.728585258220317e-08</v>
       </c>
       <c r="M13" t="n">
-        <v>5.728585258220563e-08</v>
+        <v>5.728585258220567e-08</v>
       </c>
       <c r="N13" t="n">
         <v>5.705008092990449e-08</v>
       </c>
       <c r="O13" t="n">
-        <v>5.711487302667879e-08</v>
+        <v>5.711487302667882e-08</v>
       </c>
       <c r="P13" t="n">
-        <v>5.709899091820775e-08</v>
+        <v>5.709899091820774e-08</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.692192319034179e-08</v>
+        <v>5.692192319034181e-08</v>
       </c>
       <c r="R13" t="n">
-        <v>5.728585258220308e-08</v>
+        <v>5.728585258220317e-08</v>
       </c>
       <c r="S13" t="n">
-        <v>5.728585258220308e-08</v>
+        <v>5.728585258220317e-08</v>
       </c>
       <c r="T13" t="n">
-        <v>5.728585258220308e-08</v>
+        <v>5.728585258220317e-08</v>
       </c>
       <c r="U13" t="n">
-        <v>5.713062754141911e-08</v>
+        <v>5.713062754141912e-08</v>
       </c>
       <c r="V13" t="n">
-        <v>7.409459755471486e-08</v>
+        <v>7.409459755471498e-08</v>
       </c>
       <c r="W13" t="n">
-        <v>5.728591235667102e-08</v>
+        <v>5.728591235667106e-08</v>
       </c>
       <c r="X13" t="n">
-        <v>5.694979967595657e-08</v>
+        <v>5.694979967595651e-08</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.757668520618824e-08</v>
+        <v>5.75766852061883e-08</v>
       </c>
       <c r="Z13" t="n">
         <v>5.697604690202441e-08</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.728585258220308e-08</v>
+        <v>5.728585258220317e-08</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.760356877847973e-08</v>
+        <v>5.760356877847988e-08</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="C14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="D14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="F14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>5.826154625802549e-09</v>
+        <v>5.826154625802548e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>5.829162587809595e-09</v>
+        <v>5.829162587809592e-09</v>
       </c>
       <c r="K14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="L14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="M14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="N14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="O14" t="n">
-        <v>5.826154625802549e-09</v>
+        <v>5.826154625802548e-09</v>
       </c>
       <c r="P14" t="n">
-        <v>5.826154625802549e-09</v>
+        <v>5.826154625802548e-09</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="R14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="S14" t="n">
         <v>5.946401306266932e-09</v>
       </c>
       <c r="T14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="U14" t="n">
-        <v>5.826154625802548e-09</v>
+        <v>5.826154625802547e-09</v>
       </c>
       <c r="V14" t="n">
         <v>5.830613765954596e-09</v>
       </c>
       <c r="W14" t="n">
-        <v>5.826154625802549e-09</v>
+        <v>5.826154625802548e-09</v>
       </c>
       <c r="X14" t="n">
-        <v>5.826154625802549e-09</v>
+        <v>5.826154625802548e-09</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.905802465340331e-09</v>
+        <v>5.905802465340328e-09</v>
       </c>
     </row>
     <row r="15">
@@ -7634,85 +7634,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.142390811363164e-09</v>
+        <v>7.142390811363169e-09</v>
       </c>
       <c r="C15" t="n">
-        <v>1.973920948690956e-08</v>
+        <v>1.973920948690954e-08</v>
       </c>
       <c r="D15" t="n">
-        <v>8.365132442778557e-09</v>
+        <v>8.36513244277855e-09</v>
       </c>
       <c r="E15" t="n">
         <v>1.034370852438017e-08</v>
       </c>
       <c r="F15" t="n">
-        <v>1.002387332801339e-08</v>
+        <v>1.002387332801337e-08</v>
       </c>
       <c r="G15" t="n">
-        <v>7.727467047130922e-09</v>
+        <v>7.727467047130841e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>1.378667288144176e-08</v>
+        <v>1.378667288144177e-08</v>
       </c>
       <c r="I15" t="n">
-        <v>7.840842010024287e-09</v>
+        <v>7.840842010024289e-09</v>
       </c>
       <c r="J15" t="n">
-        <v>1.067194236823851e-08</v>
+        <v>1.067194236823849e-08</v>
       </c>
       <c r="K15" t="n">
-        <v>7.057357513890822e-09</v>
+        <v>7.057357513890811e-09</v>
       </c>
       <c r="L15" t="n">
-        <v>7.522855389074346e-09</v>
+        <v>7.522855389074323e-09</v>
       </c>
       <c r="M15" t="n">
-        <v>8.454690238147048e-09</v>
+        <v>8.454690238147015e-09</v>
       </c>
       <c r="N15" t="n">
-        <v>1.785484808469716e-08</v>
+        <v>1.785484808469719e-08</v>
       </c>
       <c r="O15" t="n">
-        <v>7.322260600689581e-09</v>
+        <v>7.322260600689558e-09</v>
       </c>
       <c r="P15" t="n">
-        <v>1.06362410551907e-08</v>
+        <v>1.063624105519066e-08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.184898254017023e-08</v>
+        <v>1.184898254017024e-08</v>
       </c>
       <c r="R15" t="n">
-        <v>1.154628383019254e-08</v>
+        <v>1.154628383019256e-08</v>
       </c>
       <c r="S15" t="n">
-        <v>1.056527160849436e-08</v>
+        <v>1.056527160849437e-08</v>
       </c>
       <c r="T15" t="n">
-        <v>8.991224450566305e-09</v>
+        <v>8.991224450566308e-09</v>
       </c>
       <c r="U15" t="n">
-        <v>1.372079173645109e-08</v>
+        <v>1.372079173645108e-08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.121404288110307e-08</v>
+        <v>1.121404288110303e-08</v>
       </c>
       <c r="W15" t="n">
-        <v>3.975558875249288e-08</v>
+        <v>3.97555887524928e-08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04368183500712e-08</v>
+        <v>1.043681835007116e-08</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.598904615905695e-09</v>
+        <v>9.598904615905616e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.913507707945131e-09</v>
+        <v>8.913507707945132e-09</v>
       </c>
       <c r="AA15" t="n">
         <v>1.098836668888665e-08</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.519359228214396e-09</v>
+        <v>7.519359228214394e-09</v>
       </c>
     </row>
     <row r="16">
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.697219066094673e-09</v>
+        <v>5.69721906609468e-09</v>
       </c>
       <c r="C16" t="n">
-        <v>6.0013748956559e-09</v>
+        <v>6.001374895655902e-09</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0013748956559e-09</v>
+        <v>6.001374895655902e-09</v>
       </c>
       <c r="E16" t="n">
-        <v>5.839420888621613e-09</v>
+        <v>5.839420888621619e-09</v>
       </c>
       <c r="F16" t="n">
-        <v>5.744602989492088e-09</v>
+        <v>5.744602989492093e-09</v>
       </c>
       <c r="G16" t="n">
-        <v>5.984795748701634e-09</v>
+        <v>5.984795748701638e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>6.0013748956559e-09</v>
+        <v>6.001374895655902e-09</v>
       </c>
       <c r="I16" t="n">
-        <v>6.0013748956559e-09</v>
+        <v>6.001374895655902e-09</v>
       </c>
       <c r="J16" t="n">
         <v>5.924735018125168e-09</v>
       </c>
       <c r="K16" t="n">
-        <v>6.0013748956559e-09</v>
+        <v>6.001374895655902e-09</v>
       </c>
       <c r="L16" t="n">
-        <v>6.0013748956559e-09</v>
+        <v>6.001374895655902e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>6.001374895658438e-09</v>
+        <v>6.001374895658441e-09</v>
       </c>
       <c r="N16" t="n">
-        <v>5.765603243357319e-09</v>
+        <v>5.76560324335732e-09</v>
       </c>
       <c r="O16" t="n">
-        <v>5.750747500593826e-09</v>
+        <v>5.750747500593828e-09</v>
       </c>
       <c r="P16" t="n">
-        <v>5.73486539212275e-09</v>
+        <v>5.734865392122749e-09</v>
       </c>
       <c r="Q16" t="n">
         <v>5.637445503794593e-09</v>
       </c>
       <c r="R16" t="n">
-        <v>6.0013748956559e-09</v>
+        <v>6.001374895655902e-09</v>
       </c>
       <c r="S16" t="n">
-        <v>6.0013748956559e-09</v>
+        <v>6.001374895655902e-09</v>
       </c>
       <c r="T16" t="n">
-        <v>6.0013748956559e-09</v>
+        <v>6.001374895655902e-09</v>
       </c>
       <c r="U16" t="n">
-        <v>5.76650201533416e-09</v>
+        <v>5.766502015334161e-09</v>
       </c>
       <c r="V16" t="n">
-        <v>5.835588004339318e-09</v>
+        <v>5.835588004339315e-09</v>
       </c>
       <c r="W16" t="n">
-        <v>5.921786830586037e-09</v>
+        <v>5.921786830586036e-09</v>
       </c>
       <c r="X16" t="n">
-        <v>5.585674149871564e-09</v>
+        <v>5.585674149871568e-09</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.292207519641029e-09</v>
+        <v>6.292207519641027e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.691569215477203e-09</v>
+        <v>5.691569215477201e-09</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.0013748956559e-09</v>
+        <v>6.001374895655902e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.319091091932567e-09</v>
+        <v>6.319091091932568e-09</v>
       </c>
     </row>
   </sheetData>
@@ -9593,7 +9593,7 @@
         <v>3.372343393698739e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.589381752024728e-09</v>
+        <v>3.589381752024729e-09</v>
       </c>
       <c r="X3" t="n">
         <v>2.9972004015171e-09</v>
@@ -9645,7 +9645,7 @@
         <v>6.831076012699014e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.455668412536508e-08</v>
+        <v>6.455668412536509e-08</v>
       </c>
       <c r="L4" t="n">
         <v>6.362895997453023e-08</v>
@@ -9678,7 +9678,7 @@
         <v>6.32850442375215e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.466982828754986e-08</v>
+        <v>8.466982828754987e-08</v>
       </c>
       <c r="W4" t="n">
         <v>7.911431094457897e-08</v>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.110858326197816e-09</v>
+        <v>3.110858326197815e-09</v>
       </c>
       <c r="C6" t="n">
         <v>3.879046916493875e-09</v>
@@ -9803,7 +9803,7 @@
         <v>5.733469803686589e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>3.635838616663631e-09</v>
+        <v>3.63583861666363e-09</v>
       </c>
       <c r="F6" t="n">
         <v>3.331506988834762e-09</v>
@@ -9872,7 +9872,7 @@
         <v>9.508543607504205e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.802166814675752e-09</v>
+        <v>2.802166814675751e-09</v>
       </c>
     </row>
     <row r="7">
@@ -9948,7 +9948,7 @@
         <v>2.712775975397466e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.496932826881932e-09</v>
+        <v>2.496932826881933e-09</v>
       </c>
       <c r="Y7" t="n">
         <v>2.991290352723376e-09</v>
@@ -10112,7 +10112,7 @@
         <v>1.878744930863712e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0073840492154e-08</v>
+        <v>1.007384049215401e-08</v>
       </c>
       <c r="U9" t="n">
         <v>8.980001609555065e-09</v>
@@ -10136,7 +10136,7 @@
         <v>2.637882607868526e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.700344462376197e-09</v>
+        <v>6.700344462376198e-09</v>
       </c>
     </row>
     <row r="10">
@@ -10388,7 +10388,7 @@
         <v>8.135185917832443e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>6.423995018802107e-08</v>
+        <v>6.423995018802108e-08</v>
       </c>
       <c r="Y12" t="n">
         <v>5.938178131932334e-08</v>
@@ -10400,7 +10400,7 @@
         <v>6.696285759930777e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.729038338907988e-08</v>
+        <v>5.729038338907987e-08</v>
       </c>
     </row>
     <row r="13">
@@ -10649,7 +10649,7 @@
         <v>1.004316917418046e-08</v>
       </c>
       <c r="W15" t="n">
-        <v>2.995987050178079e-08</v>
+        <v>2.99598705017808e-08</v>
       </c>
       <c r="X15" t="n">
         <v>1.284796151147752e-08</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide ozone depletion results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide ozone depletion results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.292427044396049e-08</v>
+        <v>1.292427044396032e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.604924980809729e-08</v>
+        <v>1.60492498080973e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>4.541736865585205e-08</v>
+        <v>4.5417368655852e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.105108282630608e-09</v>
+        <v>9.105108282630593e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>3.873909518133761e-08</v>
+        <v>3.873909518133755e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.95875844179305e-09</v>
+        <v>7.958758441793e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>3.929151497885181e-08</v>
+        <v>3.929151497885162e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>5.644354165362417e-08</v>
+        <v>5.644354165362436e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.083616638915991e-08</v>
+        <v>2.08361663891599e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.003630321825947e-07</v>
+        <v>1.003630321825944e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.058032139521275e-08</v>
+        <v>2.058032139521274e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.20621994156978e-08</v>
+        <v>1.206219941569778e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>9.302173216509472e-08</v>
+        <v>9.302173216509461e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.179416169316221e-08</v>
+        <v>2.179416169316219e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>2.208569378282611e-08</v>
+        <v>2.208569378282605e-08</v>
       </c>
       <c r="Q2" t="n">
         <v>4.083853296719441e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>3.160553132099774e-08</v>
+        <v>3.160553132099767e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>2.050331497574196e-08</v>
+        <v>2.050331497574201e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>4.960175790780777e-08</v>
+        <v>4.96017579078077e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.066097008433984e-08</v>
+        <v>2.066097008433986e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.703002780965418e-08</v>
+        <v>1.703002780965413e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>5.966825851540257e-08</v>
+        <v>5.966825851540262e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.888300848048955e-08</v>
+        <v>1.888300848048946e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.37895832707043e-08</v>
+        <v>2.378958327070418e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.499804692718436e-08</v>
+        <v>1.499804692718438e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.815865634468814e-08</v>
+        <v>1.81586563446881e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.396144794172559e-09</v>
+        <v>9.396144794172554e-09</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.863640194893693e-09</v>
+        <v>3.863640194893928e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.680461934182584e-09</v>
+        <v>4.680461934182581e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.657873999583915e-09</v>
+        <v>4.657873999583702e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.134478757451881e-09</v>
+        <v>4.134478757451875e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>4.020599550000916e-09</v>
+        <v>4.020599550000912e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.822563552751141e-09</v>
+        <v>4.822563552751054e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.657873999583915e-09</v>
+        <v>4.657873999583702e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.657873999583915e-09</v>
+        <v>4.657873999583702e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.611915043928347e-09</v>
+        <v>4.611915043928271e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.657873999583915e-09</v>
+        <v>4.657873999583702e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.657873999583915e-09</v>
+        <v>4.657873999583702e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.579324227344401e-09</v>
+        <v>4.579324227344398e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>4.042209927841157e-09</v>
+        <v>4.042209927841169e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.211399759098894e-09</v>
+        <v>4.211399759098456e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.169927243405364e-09</v>
+        <v>4.16992724340503e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.7075551254761e-09</v>
+        <v>3.70755512547601e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.657873999583915e-09</v>
+        <v>4.657873999583702e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.657873999583915e-09</v>
+        <v>4.657873999583702e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.657873999583915e-09</v>
+        <v>4.657873999583702e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.272460687377125e-09</v>
+        <v>4.272460687377476e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.337641934487718e-09</v>
+        <v>4.337641934487717e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.658030086619977e-09</v>
+        <v>4.658030086619808e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.780348230210832e-09</v>
+        <v>3.780348230210963e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.451397333635666e-09</v>
+        <v>5.451397333635682e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.848886894431217e-09</v>
+        <v>3.848886894431151e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.657873999583915e-09</v>
+        <v>4.657873999583702e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.428934486328596e-09</v>
+        <v>5.42893448632859e-09</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.720901770612905e-08</v>
+        <v>6.720901770612793e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.83623908866749e-08</v>
+        <v>6.836239088667376e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.905237045114043e-08</v>
+        <v>7.905237045113919e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.575311589758807e-08</v>
+        <v>6.5753115897587e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.663933434562669e-08</v>
+        <v>7.663933434562606e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.539914688932479e-08</v>
+        <v>6.539914688932331e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.681956871927956e-08</v>
+        <v>7.681956871927865e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.307128103296813e-08</v>
+        <v>8.307128103296723e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.301555143923969e-08</v>
+        <v>7.301555143923876e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.907941960208206e-08</v>
+        <v>9.907941960208093e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.999955837597126e-08</v>
+        <v>6.999955837597053e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.684488363663916e-08</v>
+        <v>6.684488363663794e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.64036019516005e-08</v>
+        <v>9.640360195160003e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>7.044198891094145e-08</v>
+        <v>7.044198891094043e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>7.054824893428132e-08</v>
+        <v>7.054824893428018e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.738343861002801e-08</v>
+        <v>7.738343861002693e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>7.401811792936846e-08</v>
+        <v>7.401811792936764e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.997149044032911e-08</v>
+        <v>6.997149044032819e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>8.057753119789897e-08</v>
+        <v>8.057753119789788e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>7.002895387613343e-08</v>
+        <v>7.002895387613286e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.833305005627272e-08</v>
+        <v>8.833305005627266e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>8.424665246254908e-08</v>
+        <v>8.424665246254816e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.938090774940917e-08</v>
+        <v>6.938090774940806e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.116929664453233e-08</v>
+        <v>7.116929664453095e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.796488488275122e-08</v>
+        <v>6.796488488274976e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.911688990168172e-08</v>
+        <v>6.911688990168054e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.588582706747719e-08</v>
+        <v>6.588582706747597e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.390652437563629e-08</v>
+        <v>6.390652437563516e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.421860120568024e-08</v>
+        <v>6.421860120567946e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.419601327108155e-08</v>
+        <v>6.41960132710811e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.394137980373918e-08</v>
+        <v>6.394137980373789e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.398485037316335e-08</v>
+        <v>6.398485037316272e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.42560406793287e-08</v>
+        <v>6.425604067932699e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.419601327108155e-08</v>
+        <v>6.41960132710811e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.419601327108155e-08</v>
+        <v>6.41960132710811e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.710200233868065e-08</v>
+        <v>6.710200233868067e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.419601327108155e-08</v>
+        <v>6.41960132710811e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.419601327108155e-08</v>
+        <v>6.41960132710811e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.411746349884112e-08</v>
+        <v>6.411746349884003e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.39716109464239e-08</v>
+        <v>6.397161094642293e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.403327865319004e-08</v>
+        <v>6.403327865318881e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.401816240821468e-08</v>
+        <v>6.401816240821354e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.38496332006769e-08</v>
+        <v>6.384963320067637e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.419601327108155e-08</v>
+        <v>6.41960132710811e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.419601327108155e-08</v>
+        <v>6.41960132710811e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.419601327108155e-08</v>
+        <v>6.41960132710811e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.40555346445338e-08</v>
+        <v>6.405553464453263e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.370682444629423e-08</v>
+        <v>8.370682444629419e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.419607016297343e-08</v>
+        <v>6.419607016297228e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.387616543257296e-08</v>
+        <v>6.38761654325716e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.448524320832203e-08</v>
+        <v>6.448524320832108e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.390114697085973e-08</v>
+        <v>6.390114697085876e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.419601327108155e-08</v>
+        <v>6.41960132710811e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.443982549560346e-08</v>
+        <v>6.443982549560283e-08</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.4843942371929e-09</v>
+        <v>6.484394237192838e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>7.637767417738768e-09</v>
+        <v>7.637767417738775e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.832774698220438e-08</v>
+        <v>1.83277469822043e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.028492428651958e-09</v>
+        <v>5.028492428651957e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.591471087669059e-08</v>
+        <v>1.591471087669058e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.561874770715306e-09</v>
+        <v>4.5618747707153e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.609494525034343e-08</v>
+        <v>1.60949452503433e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.234665756403204e-08</v>
+        <v>2.234665756403191e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>9.230765692540804e-09</v>
+        <v>9.230765692540746e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>3.835479613314589e-08</v>
+        <v>3.835479613314585e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.274934907035126e-09</v>
+        <v>9.274934907035141e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>6.12026016770305e-09</v>
+        <v>6.120260167703041e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.567897848266431e-08</v>
+        <v>3.567897848266471e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>9.604716792331953e-09</v>
+        <v>9.604716792331974e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>9.710976815671811e-09</v>
+        <v>9.71097681567178e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.665881514109192e-08</v>
+        <v>1.665881514109194e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.329349446043241e-08</v>
+        <v>1.329349446043236e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>9.246866971393044e-09</v>
+        <v>9.246866971393068e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.985290772896285e-08</v>
+        <v>1.985290772896286e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>9.19168175752389e-09</v>
+        <v>9.191681757523928e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>7.807876141652643e-09</v>
+        <v>7.807876141652628e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.340938034393971e-08</v>
+        <v>2.340938034393977e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>8.543635630799698e-09</v>
+        <v>8.54363563079958e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.044467317559622e-08</v>
+        <v>1.044467317559586e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.240261413815078e-09</v>
+        <v>7.240261413815067e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.392266432745628e-09</v>
+        <v>8.392266432745639e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.161203598541031e-09</v>
+        <v>5.161203598541028e-09</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.181900906700107e-09</v>
+        <v>3.18190090670006e-09</v>
       </c>
       <c r="C7" t="n">
         <v>3.493977736744157e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>3.47138980214549e-09</v>
+        <v>3.471389802145567e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>3.216756334803079e-09</v>
+        <v>3.216756334803078e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>3.260226904227222e-09</v>
+        <v>3.260226904227216e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>3.418768560719238e-09</v>
+        <v>3.418768560719151e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>3.47138980214549e-09</v>
+        <v>3.471389802145567e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>3.47138980214549e-09</v>
+        <v>3.471389802145567e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>3.317216591981878e-09</v>
+        <v>3.317216591982004e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.47138980214549e-09</v>
+        <v>3.471389802145567e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>3.47138980214549e-09</v>
+        <v>3.471389802145567e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>3.392840029904982e-09</v>
+        <v>3.392840029904977e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.246987477487789e-09</v>
+        <v>3.246987477487602e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>3.196006534580592e-09</v>
+        <v>3.196006534580384e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>3.180890289605166e-09</v>
+        <v>3.180890289604972e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.125009731740814e-09</v>
+        <v>3.125009731741068e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>3.47138980214549e-09</v>
+        <v>3.471389802145567e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>3.47138980214549e-09</v>
+        <v>3.471389802145567e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>3.47138980214549e-09</v>
+        <v>3.471389802145567e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>3.218262525924383e-09</v>
+        <v>3.218262525924354e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>3.181650531674202e-09</v>
+        <v>3.181650531674199e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>3.35879804436393e-09</v>
+        <v>3.358798044363908e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>3.038893313963495e-09</v>
+        <v>3.038893313963193e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.760619739385917e-09</v>
+        <v>3.76061973938581e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.176523501923536e-09</v>
+        <v>3.176523501923516e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.47138980214549e-09</v>
+        <v>3.471389802145567e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.715202026667332e-09</v>
+        <v>3.715202026667327e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.985541328465475e-09</v>
+        <v>3.985541328465067e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.042559651381942e-08</v>
+        <v>1.042559651381943e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.028906836407762e-08</v>
+        <v>1.028906836407723e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>5.328320884418828e-09</v>
+        <v>5.328320884418825e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>4.866089789624772e-09</v>
+        <v>4.866089789624769e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>9.954293481721297e-09</v>
+        <v>9.954293481721114e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.738534137733423e-08</v>
+        <v>1.738534137733383e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>6.996986927015155e-09</v>
+        <v>6.996986927014726e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.179145210562489e-08</v>
+        <v>1.179145210562461e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.086817678742251e-08</v>
+        <v>1.08681767874221e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.251903465849952e-09</v>
+        <v>8.251903465849131e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>7.749498112907601e-09</v>
+        <v>7.749498112907562e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.456731370565362e-08</v>
+        <v>1.45673137056539e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>5.114466989463635e-09</v>
+        <v>5.11446698946302e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.151229463482604e-08</v>
+        <v>1.151229463482594e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.790049408625371e-09</v>
+        <v>6.790049408624937e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>7.523342594848108e-09</v>
+        <v>7.523342594847799e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.133318438302439e-08</v>
+        <v>1.133318438302401e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>7.456706085829925e-09</v>
+        <v>7.456706085829738e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.120813713675055e-08</v>
+        <v>1.120813713675012e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.496095348414407e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>5.170940914354333e-08</v>
+        <v>5.170940914354315e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.617368177870748e-08</v>
+        <v>1.617368177870702e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.464051627610205e-09</v>
+        <v>9.46405162760966e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.243409983663984e-08</v>
+        <v>1.243409983663963e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.395044045088352e-08</v>
+        <v>2.395044045088304e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.186599368188095e-09</v>
+        <v>4.186599368188094e-09</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.084345225287776e-09</v>
+        <v>3.084345225287245e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>3.668869458267306e-09</v>
+        <v>3.668869458267307e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>3.629942078608086e-09</v>
+        <v>3.629942078608126e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.278494578044846e-09</v>
+        <v>3.278494578044847e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.127729046728188e-09</v>
+        <v>3.127729046728186e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>3.743075140264006e-09</v>
+        <v>3.743075140263978e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>3.629942078608086e-09</v>
+        <v>3.629942078608126e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.629942078608086e-09</v>
+        <v>3.629942078608126e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.603845016032186e-09</v>
+        <v>3.603845016031902e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.629942078608086e-09</v>
+        <v>3.629942078608126e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>3.629942078608086e-09</v>
+        <v>3.629942078608126e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.582847962630645e-09</v>
+        <v>3.582847962630603e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.207013240532558e-09</v>
+        <v>3.207013240532175e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.323237756705901e-09</v>
+        <v>3.323237756705543e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.294748319491205e-09</v>
+        <v>3.294748319490706e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.977122991352959e-09</v>
+        <v>2.977122991352817e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>3.629942078608086e-09</v>
+        <v>3.629942078608126e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>3.629942078608086e-09</v>
+        <v>3.629942078608126e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>3.629942078608086e-09</v>
+        <v>3.629942078608126e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.353967744893969e-09</v>
+        <v>3.353967744893678e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.409922656302716e-09</v>
+        <v>3.409922656302714e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.630049302551597e-09</v>
+        <v>3.630049302551439e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.027128026176001e-09</v>
+        <v>3.027128026175407e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.155864148089341e-09</v>
+        <v>4.155864148089125e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.074210483743774e-09</v>
+        <v>3.074210483743484e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.629942078608086e-09</v>
+        <v>3.629942078608126e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.164650384389164e-09</v>
+        <v>4.164650384389163e-09</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.264901909471447e-08</v>
+        <v>6.2649019094714e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.502108239371107e-08</v>
+        <v>6.502108239371132e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.494658067944351e-08</v>
+        <v>6.494658067944273e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.309972266619001e-08</v>
+        <v>6.309972266619025e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.294352261566673e-08</v>
+        <v>6.294352261566685e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.48245591659498e-08</v>
+        <v>6.482455916594902e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.753308886413077e-08</v>
+        <v>6.753308886413026e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.374665565320625e-08</v>
+        <v>6.374665565320579e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.841722359289793e-08</v>
+        <v>6.84172235928981e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.515765889951831e-08</v>
+        <v>6.51576588995179e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.420405799563725e-08</v>
+        <v>6.420405799563684e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.399100828031826e-08</v>
+        <v>6.399100828031828e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.650595086875452e-08</v>
+        <v>6.650595086875449e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.306049924163381e-08</v>
+        <v>6.306049924163349e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.5392432291283e-08</v>
+        <v>6.539243229128292e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.367122935773624e-08</v>
+        <v>6.367122935773573e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.393850611335106e-08</v>
+        <v>6.393850611335055e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.532714870772023e-08</v>
+        <v>6.532714870771982e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.391421788829893e-08</v>
+        <v>6.39142178882989e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.528157045483246e-08</v>
+        <v>6.528157045483191e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.622360770440314e-08</v>
+        <v>8.62236077044032e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>8.004380851136103e-08</v>
+        <v>8.004380851136058e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.709145316845666e-08</v>
+        <v>6.709145316845622e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.464587176683675e-08</v>
+        <v>6.464587176683641e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.572841946296109e-08</v>
+        <v>6.572841946296083e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.992599038515375e-08</v>
+        <v>6.992599038515361e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.269992396921365e-08</v>
+        <v>6.269992396921373e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1534,22 +1534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.232054369748473e-08</v>
+        <v>6.232054369748462e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.255833472345738e-08</v>
+        <v>6.255833472345751e-08</v>
       </c>
       <c r="D5" t="n">
         <v>6.251940734379832e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.235258504779273e-08</v>
+        <v>6.235258504779266e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.230991053774331e-08</v>
+        <v>6.230991053774358e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.256064301629655e-08</v>
+        <v>6.256064301629651e-08</v>
       </c>
       <c r="H5" t="n">
         <v>6.251940734379832e-08</v>
@@ -1558,7 +1558,7 @@
         <v>6.251940734379832e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.543293695247789e-08</v>
+        <v>6.543293695247796e-08</v>
       </c>
       <c r="K5" t="n">
         <v>6.251940734379832e-08</v>
@@ -1567,19 +1567,19 @@
         <v>6.251940734379832e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.247231322781871e-08</v>
+        <v>6.247231322781867e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.236525474860091e-08</v>
+        <v>6.236525474860078e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.24076172199691e-08</v>
+        <v>6.24076172199688e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.239723315464431e-08</v>
+        <v>6.239723315464387e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.228146245228261e-08</v>
+        <v>6.228146245228255e-08</v>
       </c>
       <c r="R5" t="n">
         <v>6.251940734379832e-08</v>
@@ -1591,28 +1591,28 @@
         <v>6.251940734379832e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.241881793981381e-08</v>
+        <v>6.241881793981364e-08</v>
       </c>
       <c r="V5" t="n">
         <v>8.20133926067071e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.251944642566673e-08</v>
+        <v>6.25194464256666e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.229968870028685e-08</v>
+        <v>6.229968870028652e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.271109976243566e-08</v>
+        <v>6.271109976243541e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.231684970320003e-08</v>
+        <v>6.231684970320001e-08</v>
       </c>
       <c r="AA5" t="n">
         <v>6.251940734379832e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.26919238223568e-08</v>
+        <v>6.269192382235697e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.957075590102192e-09</v>
+        <v>2.957075590101648e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>5.329138889099181e-09</v>
+        <v>5.329138889099184e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>5.254637174831288e-09</v>
+        <v>5.254637174830825e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>3.40777916157801e-09</v>
+        <v>3.407779161578014e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>3.251579111054686e-09</v>
+        <v>3.251579111054685e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>5.042657958959536e-09</v>
+        <v>5.042657958958816e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.841145359518514e-09</v>
+        <v>7.841145359518001e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.054712148593972e-09</v>
+        <v>4.054712148593402e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>5.699155592538073e-09</v>
+        <v>5.69915559253802e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.46571539490606e-09</v>
+        <v>5.465715394905521e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.512114491025108e-09</v>
+        <v>4.512114491025122e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.299064775706143e-09</v>
+        <v>4.299064775706017e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.814007364142529e-09</v>
+        <v>6.814007364142242e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.278598034643607e-09</v>
+        <v>3.278598034643261e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>5.610531084292638e-09</v>
+        <v>5.610531084292645e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.979285853123928e-09</v>
+        <v>3.979285853123401e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.246562608738802e-09</v>
+        <v>4.246562608737872e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>5.635205203108112e-09</v>
+        <v>5.635205203107511e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.222274383686818e-09</v>
+        <v>4.222274383686573e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>5.499669247842131e-09</v>
+        <v>5.499669247841657e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>6.834444653546221e-09</v>
+        <v>6.834444653546226e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.026190730437073e-08</v>
+        <v>2.026190730437026e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.309551961466396e-09</v>
+        <v>7.309551961465908e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.953928262224534e-09</v>
+        <v>4.953928262224e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.036475958348739e-09</v>
+        <v>6.036475958348515e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.023404688054155e-08</v>
+        <v>1.023404688054153e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.00798046460156e-09</v>
+        <v>3.007980464601559e-09</v>
       </c>
     </row>
     <row r="7">
@@ -1710,82 +1710,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.628600192872541e-09</v>
+        <v>2.628600192872188e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.866391218845303e-09</v>
+        <v>2.866391218845304e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.827463839186189e-09</v>
+        <v>2.827463839186023e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.660641543180443e-09</v>
+        <v>2.660641543180442e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.617967033131327e-09</v>
+        <v>2.617967033131326e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.778741809306351e-09</v>
+        <v>2.778741809306155e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.827463839186189e-09</v>
+        <v>2.827463839186023e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.827463839186189e-09</v>
+        <v>2.827463839186023e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.71486895211822e-09</v>
+        <v>2.714868952117977e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.827463839186189e-09</v>
+        <v>2.827463839186023e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.827463839186189e-09</v>
+        <v>2.827463839186023e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.780369723206492e-09</v>
+        <v>2.780369723206364e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.673311243988935e-09</v>
+        <v>2.673311243988492e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.625716012978792e-09</v>
+        <v>2.62571601297855e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.615331947654139e-09</v>
+        <v>2.615331947653646e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.589518947670539e-09</v>
+        <v>2.589518947670224e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.827463839186189e-09</v>
+        <v>2.827463839186023e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.827463839186189e-09</v>
+        <v>2.827463839186023e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.827463839186189e-09</v>
+        <v>2.827463839186023e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.636916732823557e-09</v>
+        <v>2.636916732823425e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.624229555850159e-09</v>
+        <v>2.624229555850157e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.73754521867656e-09</v>
+        <v>2.737545218676323e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.517787493296744e-09</v>
+        <v>2.517787493296364e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.019156257823475e-09</v>
+        <v>3.019156257823079e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.624906198587932e-09</v>
+        <v>2.624906198587728e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.827463839186189e-09</v>
+        <v>2.827463839186023e-09</v>
       </c>
       <c r="AB7" t="n">
         <v>2.999980317744829e-09</v>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.859914352594221e-09</v>
+        <v>7.859914352594583e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.318294326386792e-08</v>
+        <v>1.318294326386836e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.739978012207455e-08</v>
+        <v>1.739978012207441e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.181341889700744e-08</v>
+        <v>1.181341889700741e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.22850209003431e-08</v>
+        <v>2.228502090034313e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.300461439687765e-09</v>
+        <v>6.300461439687513e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.682164321774093e-08</v>
+        <v>2.682164321774083e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.413022480333124e-08</v>
+        <v>3.413022480333127e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.625157685519497e-08</v>
+        <v>1.625157685519504e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.1511874150645e-08</v>
+        <v>8.151187415064489e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.673566393866775e-09</v>
+        <v>8.673566393867961e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>8.5896763802889e-09</v>
+        <v>8.589676380288745e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>5.931674251635989e-08</v>
+        <v>5.931674251635986e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39017248217704e-08</v>
+        <v>1.390172482177028e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.545118438794998e-08</v>
+        <v>1.545118438795011e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.818050895040532e-08</v>
+        <v>2.818050895040518e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>2.400197072632844e-08</v>
+        <v>2.400197072632836e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.541332368817312e-08</v>
+        <v>1.541332368817311e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.969246848017379e-08</v>
+        <v>1.969246848017368e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.195424097423276e-08</v>
+        <v>1.195424097423261e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.342172311405244e-08</v>
+        <v>1.342172311405234e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>8.021173266828509e-08</v>
+        <v>8.021173266828487e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.92028403886455e-08</v>
+        <v>1.920284038864465e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.538518233325725e-08</v>
+        <v>2.538518233325716e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.283663972149373e-08</v>
+        <v>1.283663972149368e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.424023054265995e-08</v>
+        <v>1.424023054265994e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.581872229951516e-09</v>
+        <v>8.58187222995162e-09</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.59613882631635e-09</v>
+        <v>3.596138826316368e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.348228080712066e-09</v>
+        <v>4.348228080711559e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.313040205571936e-09</v>
+        <v>4.313040205572553e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.860248007607811e-09</v>
+        <v>3.860248007607803e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.708407178241404e-09</v>
+        <v>3.708407178241405e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.461694376553524e-09</v>
+        <v>4.461694376554482e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.313040205571936e-09</v>
+        <v>4.313040205572553e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.313040205571936e-09</v>
+        <v>4.313040205572553e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.275921717827403e-09</v>
+        <v>4.275921717828057e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.313040205571936e-09</v>
+        <v>4.313040205572553e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.313040205571936e-09</v>
+        <v>4.313040205572553e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.248552467029677e-09</v>
+        <v>4.24855246702966e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.757321701038232e-09</v>
+        <v>3.75732170103785e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.910037970076758e-09</v>
+        <v>3.910037970075743e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.8726035225213e-09</v>
+        <v>3.872603522521828e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.455251343446792e-09</v>
+        <v>3.455251343446756e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.313040205571936e-09</v>
+        <v>4.313040205572553e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.313040205571936e-09</v>
+        <v>4.313040205572553e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.313040205571936e-09</v>
+        <v>4.313040205572553e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.966638700059018e-09</v>
+        <v>3.966638700058355e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.035549346328663e-09</v>
+        <v>4.035549346328765e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.313181094849996e-09</v>
+        <v>4.313181094850376e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.520956777897804e-09</v>
+        <v>3.520956777897852e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.031840935492887e-09</v>
+        <v>5.031840935493409e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.582822015333148e-09</v>
+        <v>3.582822015333784e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.313040205571936e-09</v>
+        <v>4.313040205572553e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.024687711338916e-09</v>
+        <v>5.024687711338888e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.467573052664307e-08</v>
+        <v>6.467573052664282e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.663827436648919e-08</v>
+        <v>6.663827436648886e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.815289957685901e-08</v>
+        <v>6.815289957685888e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.607157490814493e-08</v>
+        <v>6.607157490814485e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.9933883293657e-08</v>
+        <v>6.993388329365683e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.410732825190934e-08</v>
+        <v>6.410732825190936e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.158705803812714e-08</v>
+        <v>7.158705803812709e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.425095020437666e-08</v>
+        <v>7.425095020437683e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.067390038851361e-08</v>
+        <v>7.067390038851405e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.152100500805545e-08</v>
+        <v>9.152100500805538e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.497229714130226e-08</v>
+        <v>6.497229714130233e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.490073750134036e-08</v>
+        <v>6.490073750134033e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.343114015575278e-08</v>
+        <v>8.343114015575282e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.687789949613739e-08</v>
+        <v>6.687789949613724e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.744265931333701e-08</v>
+        <v>6.744265931333697e-08</v>
       </c>
       <c r="Q4" t="n">
         <v>7.208234864107621e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>7.055932052527332e-08</v>
+        <v>7.055932052527324e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.742885953285111e-08</v>
+        <v>6.742885953285096e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.898855756128027e-08</v>
+        <v>6.898855756128009e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.616806450221973e-08</v>
+        <v>6.61680645022197e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.641769955641726e-08</v>
+        <v>8.641769955641743e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>9.104711870476719e-08</v>
+        <v>9.10471187047673e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.881009387142154e-08</v>
+        <v>6.881009387142161e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.106348491350813e-08</v>
+        <v>7.106348491350803e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.648968848394721e-08</v>
+        <v>6.648968848394715e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.700128085646677e-08</v>
+        <v>6.700128085646665e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.491522453540112e-08</v>
+        <v>6.4915224535401e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.312163441509518e-08</v>
+        <v>6.312163441509486e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.34181244246924e-08</v>
+        <v>6.34181244246913e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.338293654955186e-08</v>
+        <v>6.338293654955233e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.317273750980645e-08</v>
+        <v>6.317273750980627e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.316292572956267e-08</v>
+        <v>6.316292572956249e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.343711924928932e-08</v>
+        <v>6.343711924928997e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.338293654955186e-08</v>
+        <v>6.338293654955233e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.338293654955186e-08</v>
+        <v>6.338293654955233e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.630891471618619e-08</v>
+        <v>6.630891471618618e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.338293654955186e-08</v>
+        <v>6.338293654955233e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.338293654955186e-08</v>
+        <v>6.338293654955233e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.331844881100812e-08</v>
+        <v>6.331844881100786e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.31803836802254e-08</v>
+        <v>6.318038368022581e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.323604696700614e-08</v>
+        <v>6.323604696700515e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.322240255044896e-08</v>
+        <v>6.322240255044899e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.3070282581973e-08</v>
+        <v>6.307028258197333e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.338293654955186e-08</v>
+        <v>6.338293654955233e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.338293654955186e-08</v>
+        <v>6.338293654955233e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.338293654955186e-08</v>
+        <v>6.338293654955233e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.325667726844466e-08</v>
+        <v>6.325667726844454e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.299654943609917e-08</v>
+        <v>8.299654943609897e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.338298790203909e-08</v>
+        <v>6.338298790203997e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.309423144127844e-08</v>
+        <v>6.309423144127861e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.36449309750239e-08</v>
+        <v>6.364493097502413e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.31167805938662e-08</v>
+        <v>6.31167805938656e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.338293654955186e-08</v>
+        <v>6.338293654955233e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.361867254893636e-08</v>
+        <v>6.361867254893618e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.540715806578476e-09</v>
+        <v>4.540715806578069e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>6.503259646424578e-09</v>
+        <v>6.503259646424655e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.017884856794389e-09</v>
+        <v>8.017884856794136e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>5.936560188080285e-09</v>
+        <v>5.936560188080316e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.798868573592428e-09</v>
+        <v>9.798868573592416e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.86479215822516e-09</v>
+        <v>3.864792158225067e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.145204331806248e-08</v>
+        <v>1.145204331806225e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.411593548431194e-08</v>
+        <v>1.4115935484312e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.472500818952274e-09</v>
+        <v>7.472500818952585e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>3.138599028799082e-08</v>
+        <v>3.138599028799061e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.837282421237606e-09</v>
+        <v>4.837282421237582e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.765722781275758e-09</v>
+        <v>4.76572278127576e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.329612543568817e-08</v>
+        <v>2.329612543568797e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>6.635363402453175e-09</v>
+        <v>6.635363402453219e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>7.200123219652802e-09</v>
+        <v>7.200123219652712e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.194733392101159e-08</v>
+        <v>1.19473339210112e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.04243058052087e-08</v>
+        <v>1.042430580520842e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>7.29384481278645e-09</v>
+        <v>7.293844812786206e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>8.853542841215617e-09</v>
+        <v>8.853542841215392e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>5.925528408535621e-09</v>
+        <v>5.92552840853568e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>6.412574828002044e-09</v>
+        <v>6.412574828001959e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>3.08045826110829e-08</v>
+        <v>3.080458261108327e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>8.567557777737384e-09</v>
+        <v>8.56755777773732e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.092847019344351e-08</v>
+        <v>1.092847019344328e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.354673763882559e-09</v>
+        <v>6.354673763882342e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.866266136402094e-09</v>
+        <v>6.866266136401913e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.780209815336515e-09</v>
+        <v>4.780209815336576e-09</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.986619695030491e-09</v>
+        <v>2.986619695029954e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>3.283109704627677e-09</v>
+        <v>3.283109704626151e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>3.247921829487207e-09</v>
+        <v>3.247921829488133e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>3.03772278974181e-09</v>
+        <v>3.037722789741802e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>3.027911009497982e-09</v>
+        <v>3.027911009497965e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>3.194583155605203e-09</v>
+        <v>3.194583155605968e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>3.247921829487207e-09</v>
+        <v>3.247921829488133e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>3.247921829487207e-09</v>
+        <v>3.247921829488133e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>3.107515146624361e-09</v>
+        <v>3.107515146624793e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.247921829487207e-09</v>
+        <v>3.247921829488133e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>3.247921829487207e-09</v>
+        <v>3.247921829488133e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>3.183434090943427e-09</v>
+        <v>3.183434090943421e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0453689601608e-09</v>
+        <v>3.045368960161125e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.993510873322035e-09</v>
+        <v>2.993510873321128e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.97986645676475e-09</v>
+        <v>2.97986645676498e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.935267861908373e-09</v>
+        <v>2.935267861908308e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>3.247921829487207e-09</v>
+        <v>3.247921829488133e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>3.247921829487207e-09</v>
+        <v>3.247921829488133e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>3.247921829487207e-09</v>
+        <v>3.247921829488133e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>3.014141174760457e-09</v>
+        <v>3.014141174760542e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.991424707683774e-09</v>
+        <v>2.991424707683885e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>3.140451808354951e-09</v>
+        <v>3.140451808355995e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.851695347594254e-09</v>
+        <v>2.851695347594546e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.509916254959322e-09</v>
+        <v>3.509916254959855e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.981765873801563e-09</v>
+        <v>2.981765873800948e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.247921829487207e-09</v>
+        <v>3.247921829488133e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.483657828871743e-09</v>
+        <v>3.483657828871736e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.041687027012824e-09</v>
+        <v>5.041687026999657e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>2.738017716852824e-08</v>
+        <v>2.73801771685284e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.011922815112058e-08</v>
+        <v>2.011922815110736e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.797523957435388e-08</v>
+        <v>1.797523957435401e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.387220216318087e-09</v>
+        <v>9.387220216318228e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.193023618600593e-09</v>
+        <v>6.19302361858677e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.988491646006083e-08</v>
+        <v>1.988491646004767e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.127656981690566e-08</v>
+        <v>1.127656981689243e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.338996368984239e-08</v>
+        <v>1.338996368983824e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>7.264493637989385e-09</v>
+        <v>7.264493637976079e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>3.960454710443258e-09</v>
+        <v>3.960454710429986e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>8.386247543208083e-09</v>
+        <v>8.386247543208141e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.453812299852137e-08</v>
+        <v>3.453812299850815e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>8.132611379392742e-09</v>
+        <v>8.132611379379541e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.317539604448875e-08</v>
+        <v>1.317539604447525e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.597963825961537e-08</v>
+        <v>1.597963825960221e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.552102159136502e-08</v>
+        <v>1.552102159135183e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.294747494082373e-08</v>
+        <v>1.294747494081046e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>9.135667033206293e-09</v>
+        <v>9.135667033193062e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.355392601111701e-08</v>
+        <v>1.355392601110382e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25169311422635e-08</v>
+        <v>1.251693114226372e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>7.377162662465706e-08</v>
+        <v>7.377162662464376e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.550063376711025e-08</v>
+        <v>1.550063376709701e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.42044519451498e-08</v>
+        <v>1.420445194513664e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.185439297461975e-08</v>
+        <v>1.185439297460656e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.121678528366088e-08</v>
+        <v>1.121678528364762e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.426068658105992e-09</v>
+        <v>7.426068658106128e-09</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.285385297616588e-09</v>
+        <v>3.285385297603481e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>3.983281934529782e-09</v>
+        <v>3.983281934529932e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>3.906033026303064e-09</v>
+        <v>3.906033026289039e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.529555070852799e-09</v>
+        <v>3.529555070852948e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.349891105413196e-09</v>
+        <v>3.349891105413342e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.03472837584219e-09</v>
+        <v>4.03472837583562e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>3.906033026303064e-09</v>
+        <v>3.906033026289039e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.906033026303064e-09</v>
+        <v>3.906033026289039e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.874862931039188e-09</v>
+        <v>3.874862931041476e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.906033026303064e-09</v>
+        <v>3.906033026289039e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>3.906033026303064e-09</v>
+        <v>3.906033026289039e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.853421988264471e-09</v>
+        <v>3.853421988264617e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.42492720396753e-09</v>
+        <v>3.424927203967648e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.557139260326273e-09</v>
+        <v>3.557139260321285e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.524730890722922e-09</v>
+        <v>3.524730890713716e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.163413853842815e-09</v>
+        <v>3.163413853837256e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>3.906033026303064e-09</v>
+        <v>3.906033026289039e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>3.906033026303064e-09</v>
+        <v>3.906033026289039e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>3.906033026303064e-09</v>
+        <v>3.906033026289039e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.599342258948091e-09</v>
+        <v>3.599342258939496e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.659169586463225e-09</v>
+        <v>3.659169586463422e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.906154999447308e-09</v>
+        <v>3.906154999431534e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.220297450247391e-09</v>
+        <v>3.220297450246053e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.516695140957212e-09</v>
+        <v>4.516695140943946e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.273856447574585e-09</v>
+        <v>3.273856447561558e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.906033026303064e-09</v>
+        <v>3.906033026289039e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.52450807775002e-09</v>
+        <v>4.524508077750163e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.320578944517596e-08</v>
+        <v>6.320578944516227e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.139699937824406e-08</v>
+        <v>7.139699937824415e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.870137613548648e-08</v>
+        <v>6.870137613547285e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.789068307824085e-08</v>
+        <v>6.7890683078241e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.476923204743116e-08</v>
+        <v>6.476923204743126e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.362543811313283e-08</v>
+        <v>6.362543811311902e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.861597227552202e-08</v>
+        <v>6.861597227550831e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.547833100840174e-08</v>
+        <v>6.547833100838812e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.917611492472281e-08</v>
+        <v>6.917611492471853e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.401597635336387e-08</v>
+        <v>6.401597635335016e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.281169296225724e-08</v>
+        <v>6.281169296224348e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.439140754705015e-08</v>
+        <v>6.439140754705025e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.395689399215236e-08</v>
+        <v>7.395689399213873e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.433239507615218e-08</v>
+        <v>6.433239507613847e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.617043087121252e-08</v>
+        <v>6.617043087119872e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.71925442295515e-08</v>
+        <v>6.719254422953791e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.702538383932303e-08</v>
+        <v>6.702538383930942e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.608735630531134e-08</v>
+        <v>6.608735630529759e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.469799708349295e-08</v>
+        <v>6.469799708347936e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.630840059912517e-08</v>
+        <v>6.630840059911159e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.55475367636391e-08</v>
+        <v>8.554753676363953e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>8.825704536081936e-08</v>
+        <v>8.825704536080571e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.701795271678813e-08</v>
+        <v>6.701795271677448e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.6545509663219e-08</v>
+        <v>6.654550966320532e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.568894076424647e-08</v>
+        <v>6.568894076423276e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.545654024805946e-08</v>
+        <v>6.54565402480458e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.405590272158135e-08</v>
+        <v>6.405590272158151e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.256563808834713e-08</v>
+        <v>6.256563808833355e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.286910580566648e-08</v>
+        <v>6.286910580566656e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.279185689743975e-08</v>
+        <v>6.279185689743456e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.262540070650648e-08</v>
+        <v>6.262540070650645e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.256869648040399e-08</v>
+        <v>6.256869648040412e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.283876484112962e-08</v>
+        <v>6.283876484112438e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.279185689743975e-08</v>
+        <v>6.279185689743456e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.279185689743975e-08</v>
+        <v>6.279185689743456e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.57079724300933e-08</v>
+        <v>6.570797243008433e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.279185689743975e-08</v>
+        <v>6.279185689743456e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.279185689743975e-08</v>
+        <v>6.279185689743456e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.273924585939815e-08</v>
+        <v>6.27392458593983e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.261649947462826e-08</v>
+        <v>6.261649947461988e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.266468921665875e-08</v>
+        <v>6.266468921665386e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.265287674649654e-08</v>
+        <v>6.265287674649036e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.252118092935261e-08</v>
+        <v>6.252118092934542e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.279185689743975e-08</v>
+        <v>6.279185689743456e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.279185689743975e-08</v>
+        <v>6.279185689743456e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.279185689743975e-08</v>
+        <v>6.279185689743456e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.268007171408366e-08</v>
+        <v>6.268007171406967e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.231898668963746e-08</v>
+        <v>8.231898668963752e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.27919013552186e-08</v>
+        <v>6.279190135521003e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.254191433228122e-08</v>
+        <v>6.254191433227424e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.30144360674746e-08</v>
+        <v>6.3014436067461e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.256143595788545e-08</v>
+        <v>6.256143595787795e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.279185689743975e-08</v>
+        <v>6.279185689743456e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.299831796188615e-08</v>
+        <v>6.299831796188625e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.401692317407304e-09</v>
+        <v>3.401692317393732e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.159290225047546e-08</v>
+        <v>1.159290225047561e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.897279007717861e-09</v>
+        <v>8.897279007704251e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>8.086585950472305e-09</v>
+        <v>8.08658595047245e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.965134919662535e-09</v>
+        <v>4.965134919662694e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.724417147525503e-09</v>
+        <v>3.724417147511626e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.81187514775338e-09</v>
+        <v>8.811875147739787e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>5.674233880633133e-09</v>
+        <v>5.674233880619529e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>6.331559984194344e-09</v>
+        <v>6.331559984190418e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.211879225595224e-09</v>
+        <v>4.211879225581596e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.007595834488592e-09</v>
+        <v>3.007595834474951e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.587310419281576e-09</v>
+        <v>4.587310419281704e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.415279686438377e-08</v>
+        <v>1.415279686437017e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>4.431374110544847e-09</v>
+        <v>4.4313741105312e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>6.269409905605182e-09</v>
+        <v>6.269409905591397e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.388447101782915e-09</v>
+        <v>7.388447101769338e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>7.221286711554515e-09</v>
+        <v>7.221286711540875e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>6.28325917754269e-09</v>
+        <v>6.283259177529103e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.89389995572446e-09</v>
+        <v>4.893899955710851e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>6.40737963351785e-09</v>
+        <v>6.407379633504229e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.988617251894569e-09</v>
+        <v>5.988617251894794e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.835602439521206e-08</v>
+        <v>2.835602439519841e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.116931751180786e-09</v>
+        <v>7.116931751167157e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.741412535450345e-09</v>
+        <v>6.741412535436796e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.88484363647787e-09</v>
+        <v>5.884843636464253e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.652443120290835e-09</v>
+        <v>5.652443120277215e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.251805593812796e-09</v>
+        <v>4.251805593812944e-09</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.761540960578569e-09</v>
+        <v>2.761540960564965e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>3.065008677897896e-09</v>
+        <v>3.065008677898064e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.987759769671158e-09</v>
+        <v>2.98775976966607e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.82130357873784e-09</v>
+        <v>2.821303578737995e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.764599352635406e-09</v>
+        <v>2.764599352635562e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.937743875522322e-09</v>
+        <v>2.937743875517087e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.987759769671158e-09</v>
+        <v>2.98775976966607e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.987759769671158e-09</v>
+        <v>2.98775976966607e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.863417489564873e-09</v>
+        <v>2.863417489556414e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.987759769671158e-09</v>
+        <v>2.98775976966607e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.987759769671158e-09</v>
+        <v>2.98775976966607e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.935148731629621e-09</v>
+        <v>2.935148731629777e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.812402346859652e-09</v>
+        <v>2.812402346851372e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.763668251051394e-09</v>
+        <v>2.763668251046551e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.751855780889206e-09</v>
+        <v>2.751855780883095e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.717083801584045e-09</v>
+        <v>2.717083801576885e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.987759769671158e-09</v>
+        <v>2.98775976966607e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.987759769671158e-09</v>
+        <v>2.98775976966607e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.987759769671158e-09</v>
+        <v>2.98775976966607e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.779050748476346e-09</v>
+        <v>2.779050748462376e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.760067177892949e-09</v>
+        <v>2.760067177893137e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.890880389611241e-09</v>
+        <v>2.890880389602713e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.640893366673845e-09</v>
+        <v>2.640893366666896e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.210338939706008e-09</v>
+        <v>3.210338939692406e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.757338830116821e-09</v>
+        <v>2.757338830109457e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.987759769671158e-09</v>
+        <v>2.98775976966607e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.194220834117592e-09</v>
+        <v>3.19422083411773e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.871819065708564e-09</v>
+        <v>5.871819065707111e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>2.980909315611521e-08</v>
+        <v>2.980909315611519e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>8.186548568280559e-09</v>
+        <v>8.186548568279123e-09</v>
       </c>
       <c r="E2" t="n">
         <v>1.188550680838823e-08</v>
@@ -3337,70 +3337,70 @@
         <v>1.131072064724184e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.130185010440753e-09</v>
+        <v>7.130185010439326e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.844987753356197e-08</v>
+        <v>1.844987753356051e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.194032650418379e-09</v>
+        <v>7.194032650416933e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.267303757674173e-08</v>
+        <v>1.267303757674114e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>5.710845498355185e-09</v>
+        <v>5.710845498353895e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>6.592063277637308e-09</v>
+        <v>6.592063277636159e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>8.31299413493926e-09</v>
+        <v>8.312994134939367e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.615119801097699e-08</v>
+        <v>2.615119801097556e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>6.363102830434981e-09</v>
+        <v>6.363102830433532e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.263668355419038e-08</v>
+        <v>1.263668355418893e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.478170358368332e-08</v>
+        <v>1.478170358368186e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.420867522153884e-08</v>
+        <v>1.42086752215374e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.235155522692475e-08</v>
+        <v>1.235155522692333e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>9.371781494449351e-09</v>
+        <v>9.371781494447903e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.84759387824819e-08</v>
+        <v>1.847593878248045e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36610816072484e-08</v>
+        <v>1.366108160724838e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.776150426760204e-08</v>
+        <v>6.776150426760053e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.225916339198816e-08</v>
+        <v>1.225916339198711e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.052215960434478e-08</v>
+        <v>1.052215960434404e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.224658641699075e-09</v>
+        <v>9.224658641698718e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.315250175545956e-08</v>
+        <v>1.315250175545811e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.561877635736307e-09</v>
+        <v>6.561877635736304e-09</v>
       </c>
     </row>
     <row r="3">
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.136014878535669e-09</v>
+        <v>3.13601487853451e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>3.802478011246252e-09</v>
+        <v>3.802478011246249e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>3.711801662903506e-09</v>
+        <v>3.711801662901763e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.358597107528722e-09</v>
+        <v>3.358597107528717e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.209783337541625e-09</v>
+        <v>3.209783337541621e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>3.831194803417747e-09</v>
+        <v>3.831194803415608e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>3.711801662903506e-09</v>
+        <v>3.711801662901763e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.711801662903506e-09</v>
+        <v>3.711801662901763e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.686265043762215e-09</v>
+        <v>3.686265043761898e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.711801662903506e-09</v>
+        <v>3.711801662901763e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>3.711801662903506e-09</v>
+        <v>3.711801662901763e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.668708493174151e-09</v>
+        <v>3.668708493174257e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.265470577557939e-09</v>
+        <v>3.265470577557142e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.388126234390309e-09</v>
+        <v>3.388126234389033e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.358060369210247e-09</v>
+        <v>3.358060369208264e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.022859634144374e-09</v>
+        <v>3.022859634143533e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>3.711801662903506e-09</v>
+        <v>3.711801662901763e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>3.711801662903506e-09</v>
+        <v>3.711801662901763e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>3.711801662903506e-09</v>
+        <v>3.711801662901763e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.417950556333172e-09</v>
+        <v>3.417950556331802e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.479316415295184e-09</v>
+        <v>3.479316415295139e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.711914819861738e-09</v>
+        <v>3.711914819860545e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.07563163603128e-09</v>
+        <v>3.075631636030641e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.262366751841091e-09</v>
+        <v>4.26236675184009e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.125319343540359e-09</v>
+        <v>3.1253193435389e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.711801662903506e-09</v>
+        <v>3.711801662901763e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.28969192236312e-09</v>
+        <v>4.289691922363113e-09</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.329186140722307e-08</v>
+        <v>6.329186140722194e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.207434261166036e-08</v>
+        <v>7.207434261166013e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.413555312998449e-08</v>
+        <v>6.413555312998329e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.54541555439018e-08</v>
+        <v>6.545415554390157e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.526415194440255e-08</v>
+        <v>6.526415194440235e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.375052101759898e-08</v>
+        <v>6.375052101759782e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.787641601973612e-08</v>
+        <v>6.787641601973496e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.377379273263407e-08</v>
+        <v>6.377379273263282e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.870034719784134e-08</v>
+        <v>6.870034719784057e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.323318843217013e-08</v>
+        <v>6.323318843216873e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.355438196493623e-08</v>
+        <v>6.355438196493548e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.415425483884185e-08</v>
+        <v>6.415425483884161e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.068345690028305e-08</v>
+        <v>7.068345690028183e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.347092857052065e-08</v>
+        <v>6.34709285705194e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.575757507622512e-08</v>
+        <v>6.575757507622409e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.653940968887855e-08</v>
+        <v>6.65394096888774e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.63305475797157e-08</v>
+        <v>6.633054757971452e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.565364914908334e-08</v>
+        <v>6.565364914908162e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.456755661386532e-08</v>
+        <v>6.45675566138641e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.788591503894084e-08</v>
+        <v>6.788591503893957e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.574551506338997e-08</v>
+        <v>8.574551506339005e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>8.584992491793783e-08</v>
+        <v>8.584992491793667e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.561997341016787e-08</v>
+        <v>6.561997341016711e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.498685592650002e-08</v>
+        <v>6.498685592649942e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.451393206164205e-08</v>
+        <v>6.451393206164081e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.594558475354477e-08</v>
+        <v>6.594558475354354e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.352840243214104e-08</v>
+        <v>6.352840243214091e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.229469290643349e-08</v>
+        <v>6.229469290643218e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.259523677644896e-08</v>
+        <v>6.259523677644873e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.250456042810563e-08</v>
+        <v>6.250456042810425e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.234619708596749e-08</v>
+        <v>6.234619708596725e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.231145542102535e-08</v>
+        <v>6.231145542102521e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.254807782583834e-08</v>
+        <v>6.254807782583658e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.250456042810563e-08</v>
+        <v>6.250456042810425e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.250456042810563e-08</v>
+        <v>6.250456042810425e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.542477413758126e-08</v>
+        <v>6.542477413758059e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.250456042810563e-08</v>
+        <v>6.250456042810425e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.250456042810563e-08</v>
+        <v>6.250456042810425e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.24614672583738e-08</v>
+        <v>6.246146725837371e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.234187798858239e-08</v>
+        <v>6.23418779885803e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.23865845352015e-08</v>
+        <v>6.238658453520015e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.237562588039373e-08</v>
+        <v>6.237562588039296e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.225344914858948e-08</v>
+        <v>6.225344914858763e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.250456042810563e-08</v>
+        <v>6.250456042810425e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.250456042810563e-08</v>
+        <v>6.250456042810425e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.250456042810563e-08</v>
+        <v>6.250456042810425e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.239745515033528e-08</v>
+        <v>6.239745515033341e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.203438121124618e-08</v>
+        <v>8.203438121124626e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.250460167248841e-08</v>
+        <v>6.250460167248701e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.22726839235961e-08</v>
+        <v>6.227268392359535e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.270523493796202e-08</v>
+        <v>6.270523493796062e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.229079450952143e-08</v>
+        <v>6.229079450951956e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.250456042810563e-08</v>
+        <v>6.250456042810425e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.270021742096823e-08</v>
+        <v>6.270021742096809e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.64991234360716e-09</v>
+        <v>3.649912343605579e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.243239354804389e-08</v>
+        <v>1.243239354804391e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.493604066368526e-09</v>
+        <v>4.493604066366955e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>5.812206480285258e-09</v>
+        <v>5.812206480285261e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.622202880786039e-09</v>
+        <v>5.622202880786034e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.015944465061936e-09</v>
+        <v>4.015944465060331e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.234466956120189e-09</v>
+        <v>8.234466956118607e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.131843669018091e-09</v>
+        <v>4.131843669016517e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>6.023518465155685e-09</v>
+        <v>6.023518465155148e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>3.591239368553868e-09</v>
+        <v>3.5912393685524e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.912432901320557e-09</v>
+        <v>3.912432901319182e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.512305775225265e-09</v>
+        <v>4.512305775225212e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.104150783666712e-08</v>
+        <v>1.104150783666556e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.736352017983512e-09</v>
+        <v>3.736352017981949e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>6.022998523688223e-09</v>
+        <v>6.022998523686583e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.897460625262639e-09</v>
+        <v>6.897460625261069e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>6.688598516099738e-09</v>
+        <v>6.688598516098163e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>6.011700085467259e-09</v>
+        <v>6.011700085465325e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.925607550249361e-09</v>
+        <v>4.925607550247783e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>8.151338486403669e-09</v>
+        <v>8.151338486402109e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>6.362813817603665e-09</v>
+        <v>6.362813817603662e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.61153483654007e-08</v>
+        <v>2.611534836539911e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.885396857629879e-09</v>
+        <v>5.885396857629579e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.344906862884128e-09</v>
+        <v>5.34490686288314e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.871982998026379e-09</v>
+        <v>4.871982998024462e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.303635689928841e-09</v>
+        <v>6.303635689927267e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.886453368524567e-09</v>
+        <v>3.886453368524566e-09</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.652743842815877e-09</v>
+        <v>2.652743842815878e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.953287712832448e-09</v>
+        <v>2.953287712832446e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.862611364489758e-09</v>
+        <v>2.86261136448796e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.704248022350926e-09</v>
+        <v>2.704248022350921e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.669506357408915e-09</v>
+        <v>2.669506357408909e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.813501273299877e-09</v>
+        <v>2.813501273299031e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.862611364489758e-09</v>
+        <v>2.86261136448796e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.862611364489758e-09</v>
+        <v>2.86261136448796e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.747945404895491e-09</v>
+        <v>2.74794540489516e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.862611364489758e-09</v>
+        <v>2.86261136448796e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.862611364489758e-09</v>
+        <v>2.86261136448796e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.819518194757292e-09</v>
+        <v>2.819518194757215e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.699928924964794e-09</v>
+        <v>2.699928924964062e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.652007982664114e-09</v>
+        <v>2.65200798266266e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6410493278568e-09</v>
+        <v>2.641049327855484e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.611500084972408e-09</v>
+        <v>2.611500084971331e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.862611364489758e-09</v>
+        <v>2.86261136448796e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.862611364489758e-09</v>
+        <v>2.86261136448796e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.862611364489758e-09</v>
+        <v>2.86261136448796e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.662878597798065e-09</v>
+        <v>2.662878597795928e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.651679965459911e-09</v>
+        <v>2.651679965459931e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.770025119950777e-09</v>
+        <v>2.770025119949496e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.538107371059397e-09</v>
+        <v>2.538107371057865e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.063285874345695e-09</v>
+        <v>3.063285874344299e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.648845445904889e-09</v>
+        <v>2.648845445903292e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.862611364489758e-09</v>
+        <v>2.86261136448796e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.058268357351775e-09</v>
+        <v>3.058268357351767e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.68778742381196e-09</v>
+        <v>8.687787423811972e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>4.465768778175376e-09</v>
+        <v>4.465768778175401e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>2.956785789082318e-08</v>
+        <v>2.956785789082321e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.228342167832649e-08</v>
+        <v>1.228342167832646e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.066142267765111e-09</v>
+        <v>9.066142267765133e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.902432527589296e-09</v>
+        <v>6.902432527589326e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.167487466719422e-08</v>
+        <v>2.167487466719425e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.827430898242744e-08</v>
+        <v>1.827430898242743e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.418664834736574e-08</v>
+        <v>1.418664834736577e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>4.173070090062476e-08</v>
+        <v>4.173070090062482e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.919567243256194e-08</v>
+        <v>1.919567243256195e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>7.765997198722806e-09</v>
+        <v>7.765997198722789e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.788124911449947e-08</v>
+        <v>3.788124911449951e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.060153901765335e-08</v>
+        <v>1.060153901765334e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.280482223122764e-08</v>
+        <v>1.280482223122749e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.884864389178051e-08</v>
+        <v>1.884864389178058e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.425478780403341e-08</v>
+        <v>1.425478780403344e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>2.061726772780025e-08</v>
+        <v>2.06172677278003e-08</v>
       </c>
       <c r="T2" t="n">
         <v>1.371342543551564e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.590633365234865e-08</v>
+        <v>2.590633365234864e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>9.066882008467201e-09</v>
+        <v>9.066882008467256e-09</v>
       </c>
       <c r="W2" t="n">
         <v>7.131012089193803e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>2.472019894815853e-08</v>
+        <v>2.472019894815857e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.502841972323117e-08</v>
+        <v>1.502841972323118e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.230859493033497e-08</v>
+        <v>1.230859493033509e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.578428375611781e-08</v>
+        <v>1.578428375611784e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.292794665824241e-09</v>
+        <v>9.292794665824318e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.340936003708289e-09</v>
+        <v>3.340936003708311e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>3.992703181312234e-09</v>
+        <v>3.99270318131229e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>3.974320874162119e-09</v>
+        <v>3.974320874162197e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.576640406847664e-09</v>
+        <v>3.576640406847705e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.402751176251303e-09</v>
+        <v>3.402751176251343e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.105657353010198e-09</v>
+        <v>4.105657353010286e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>3.974320874162119e-09</v>
+        <v>3.974320874162197e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.974320874162119e-09</v>
+        <v>3.974320874162197e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.938312381448086e-09</v>
+        <v>3.938312381448153e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.974320874162119e-09</v>
+        <v>3.974320874162197e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>3.974320874162119e-09</v>
+        <v>3.974320874162197e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.916375909520164e-09</v>
+        <v>3.916375909520219e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.483341636041692e-09</v>
+        <v>3.483341636041689e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.61826699273423e-09</v>
+        <v>3.618266992734291e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.585193527665661e-09</v>
+        <v>3.585193527665707e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.216461420881613e-09</v>
+        <v>3.216461420881653e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>3.974320874162119e-09</v>
+        <v>3.974320874162197e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>3.974320874162119e-09</v>
+        <v>3.974320874162197e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>3.974320874162119e-09</v>
+        <v>3.974320874162197e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.657682833771905e-09</v>
+        <v>3.65768283377194e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.709651300792306e-09</v>
+        <v>3.709651300792293e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.974445350408491e-09</v>
+        <v>3.974445350408533e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.274512401573587e-09</v>
+        <v>3.27451240157361e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.591265534493595e-09</v>
+        <v>4.591265534493618e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.329170554715751e-09</v>
+        <v>3.329170554715762e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.974320874162119e-09</v>
+        <v>3.974320874162197e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.608929643288942e-09</v>
+        <v>4.608929643288995e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.463204156606135e-08</v>
+        <v>6.463204156606143e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.310484751922275e-08</v>
+        <v>6.310484751922271e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.224258206512051e-08</v>
+        <v>7.224258206512061e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.590420932490039e-08</v>
+        <v>6.590420932490063e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.47465232715416e-08</v>
+        <v>6.474652327154163e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.398130067108394e-08</v>
+        <v>6.398130067108391e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.936568236419627e-08</v>
+        <v>6.936568236419636e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.812621610355712e-08</v>
+        <v>6.812621610355722e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.951295344893552e-08</v>
+        <v>6.951295344893548e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.667579551887975e-08</v>
+        <v>7.667579551887989e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.846204226193529e-08</v>
+        <v>6.846204226193527e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.425923514776766e-08</v>
+        <v>6.425923514776764e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.527271554538217e-08</v>
+        <v>7.527271554538224e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.53295815496107e-08</v>
+        <v>6.532958154961077e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.613265240870072e-08</v>
+        <v>6.61326524087008e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.833555443383526e-08</v>
+        <v>6.833555443383537e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.666114783363318e-08</v>
+        <v>6.666114783363325e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.898019705383485e-08</v>
+        <v>6.898019705383491e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.646382760730625e-08</v>
+        <v>6.646382760730638e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>7.090799947598491e-08</v>
+        <v>7.090799947598505e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.406219320277952e-08</v>
+        <v>8.406219320277922e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>8.745714676662747e-08</v>
+        <v>8.745714676662763e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>7.047566730460455e-08</v>
+        <v>7.047566730460469e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.694312758373608e-08</v>
+        <v>6.694312758373611e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.595178338452064e-08</v>
+        <v>6.595178338452072e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.721863114791981e-08</v>
+        <v>6.721863114791968e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.483539144934657e-08</v>
+        <v>6.483539144934665e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.268317700933266e-08</v>
+        <v>6.268317700933291e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.293242066418275e-08</v>
+        <v>6.293242066418287e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.291403835703267e-08</v>
+        <v>6.291403835703262e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.273068979163406e-08</v>
+        <v>6.273068979163415e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.268228372158062e-08</v>
+        <v>6.268228372158071e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.296190896134187e-08</v>
+        <v>6.2961908961342e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.291403835703267e-08</v>
+        <v>6.291403835703262e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.291403835703267e-08</v>
+        <v>6.291403835703262e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.577755533139507e-08</v>
+        <v>6.57775553313952e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.291403835703267e-08</v>
+        <v>6.291403835703262e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.291403835703267e-08</v>
+        <v>6.291403835703262e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.285609339238866e-08</v>
+        <v>6.285609339238884e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.273508219010698e-08</v>
+        <v>6.273508219010709e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.278426089824783e-08</v>
+        <v>6.278426089824802e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.277220600859868e-08</v>
+        <v>6.277220600859864e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.263780748554681e-08</v>
+        <v>6.263780748554694e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.291403835703267e-08</v>
+        <v>6.291403835703262e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.291403835703267e-08</v>
+        <v>6.291403835703262e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.291403835703267e-08</v>
+        <v>6.291403835703262e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.279862750946206e-08</v>
+        <v>6.279862750946202e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.210954551761105e-08</v>
+        <v>8.210954551761101e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.291408372716263e-08</v>
+        <v>6.291408372716276e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.265896638634012e-08</v>
+        <v>6.265896638634015e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.313890744119344e-08</v>
+        <v>6.31389074411936e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.267888864133194e-08</v>
+        <v>6.267888864133209e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.291403835703267e-08</v>
+        <v>6.291403835703262e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.312817764935248e-08</v>
+        <v>6.312817764935254e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.758550486224389e-09</v>
+        <v>4.758550486224388e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>3.23135643938571e-09</v>
+        <v>3.231356439385729e-09</v>
       </c>
       <c r="D6" t="n">
         <v>1.236909098528364e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.030718245063619e-09</v>
+        <v>6.030718245063615e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.873032191704668e-09</v>
+        <v>4.873032191704677e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.005551876978017e-09</v>
+        <v>4.005551876978074e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>9.492191284359334e-09</v>
+        <v>9.492191284359396e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>8.252725023720105e-09</v>
+        <v>8.252725023720196e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>6.641537371386688e-09</v>
+        <v>6.641537371386735e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.680230443904286e-08</v>
+        <v>1.680230443904285e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.588551182098287e-09</v>
+        <v>8.588551182098294e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.385744067930594e-09</v>
+        <v>4.385744067930693e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.539922446554519e-08</v>
+        <v>1.539922446554523e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.35383275550498e-09</v>
+        <v>5.353832755504974e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>6.156903614595133e-09</v>
+        <v>6.156903614595022e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.462063353998299e-09</v>
+        <v>8.462063353998352e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>6.787656753796209e-09</v>
+        <v>6.787656753796206e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>9.106705973997878e-09</v>
+        <v>9.106705973997916e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>6.590336527469343e-09</v>
+        <v>6.590336527469357e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.093225068187925e-08</v>
+        <v>1.093225068187924e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.747250282961381e-09</v>
+        <v>4.747250282961618e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.748139797252177e-08</v>
+        <v>2.748139797252179e-08</v>
       </c>
       <c r="X6" t="n">
         <v>1.049991851049886e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.069636503899137e-09</v>
+        <v>7.069636503899136e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.078292304683669e-09</v>
+        <v>6.078292304683693e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.345140068082717e-09</v>
+        <v>7.34514006808273e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.961900369509648e-09</v>
+        <v>4.961900369509682e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.809685929495901e-09</v>
+        <v>2.809685929495958e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>3.058929584345814e-09</v>
+        <v>3.058929584345823e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>3.040547277195715e-09</v>
+        <v>3.040547277195686e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.857198711797178e-09</v>
+        <v>2.857198711797192e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.808792641743663e-09</v>
+        <v>2.808792641743685e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.986160167236194e-09</v>
+        <v>2.986160167236265e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>3.040547277195715e-09</v>
+        <v>3.040547277195686e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>3.040547277195715e-09</v>
+        <v>3.040547277195686e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.906139253846412e-09</v>
+        <v>2.90613925384645e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.040547277195715e-09</v>
+        <v>3.040547277195686e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>3.040547277195715e-09</v>
+        <v>3.040547277195686e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.982602312551803e-09</v>
+        <v>2.982602312551816e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.861591110270056e-09</v>
+        <v>2.861591110270057e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.808512104142141e-09</v>
+        <v>2.808512104142221e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.796457214492898e-09</v>
+        <v>2.796457214492924e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.764316405709929e-09</v>
+        <v>2.764316405709954e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>3.040547277195715e-09</v>
+        <v>3.040547277195686e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>3.040547277195715e-09</v>
+        <v>3.040547277195686e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>3.040547277195715e-09</v>
+        <v>3.040547277195686e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.822878715356233e-09</v>
+        <v>2.822878715356243e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.794602597792988e-09</v>
+        <v>2.794602597792995e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.938334933057012e-09</v>
+        <v>2.938334933056993e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.6832175922343e-09</v>
+        <v>2.683217592234313e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.265416361356531e-09</v>
+        <v>3.265416361356597e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.805397561494972e-09</v>
+        <v>2.805397561495021e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.040547277195715e-09</v>
+        <v>3.040547277195686e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.254686569515477e-09</v>
+        <v>3.254686569515528e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.435659406594329e-09</v>
+        <v>4.435659406594254e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.484272322086896e-09</v>
+        <v>6.484272322086902e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.16309844251429e-08</v>
+        <v>1.163098442514281e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>5.971592538469357e-09</v>
+        <v>5.971592538469346e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>5.103997249534807e-09</v>
+        <v>5.103997249534806e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.168743494101993e-08</v>
+        <v>1.168743494101969e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.039815270834619e-08</v>
+        <v>2.03981527083461e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>8.655242594077398e-09</v>
+        <v>8.655242594077344e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.167084689600295e-08</v>
+        <v>1.167084689600287e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>9.287583937409705e-09</v>
+        <v>9.287583937409627e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>6.742305366751244e-09</v>
+        <v>6.742305366751164e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>7.489590780623395e-09</v>
+        <v>7.489590780623378e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.35605366361549e-08</v>
+        <v>1.356053663615485e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>6.408768121122727e-09</v>
+        <v>6.408768121122648e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>8.406578648492884e-09</v>
+        <v>8.406578648492798e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.057937247364338e-09</v>
+        <v>7.057937247364348e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>8.620447194029274e-09</v>
+        <v>8.620447194029179e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.492447606616516e-08</v>
+        <v>1.492447606616508e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>6.816553320244949e-09</v>
+        <v>6.816553320244943e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>5.79874757025312e-09</v>
+        <v>5.798747570253037e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.145426030802351e-08</v>
+        <v>1.145426030802343e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>4.922749015763345e-08</v>
+        <v>4.922749015763328e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.683353254016655e-08</v>
+        <v>1.68335325401665e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.63670262947246e-09</v>
+        <v>7.636702629472376e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.578302649521482e-09</v>
+        <v>9.578302649521391e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.198817351724792e-08</v>
+        <v>2.198817351724784e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.645180597250273e-09</v>
+        <v>3.645180597250269e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.053398382198541e-09</v>
+        <v>3.053398382198632e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>3.623096802334794e-09</v>
+        <v>3.623096802334718e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>3.589276438074217e-09</v>
+        <v>3.589276438074113e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.249100585671012e-09</v>
+        <v>3.249100585671004e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.100765147582719e-09</v>
+        <v>3.100765147582712e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>3.700394243769957e-09</v>
+        <v>3.700394243769969e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>3.589276438074217e-09</v>
+        <v>3.589276438074113e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.589276438074217e-09</v>
+        <v>3.589276438074113e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.562962304501373e-09</v>
+        <v>3.562962304501309e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.589276438074217e-09</v>
+        <v>3.589276438074113e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>3.589276438074217e-09</v>
+        <v>3.589276438074113e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.545851466963687e-09</v>
+        <v>3.545851466963676e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.173881293943906e-09</v>
+        <v>3.173881293943943e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.288035485623549e-09</v>
+        <v>3.288035485623442e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.260053534969462e-09</v>
+        <v>3.260053534969529e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.948086113773624e-09</v>
+        <v>2.948086113773712e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>3.589276438074217e-09</v>
+        <v>3.589276438074113e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>3.589276438074217e-09</v>
+        <v>3.589276438074113e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>3.589276438074217e-09</v>
+        <v>3.589276438074113e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.319261976164252e-09</v>
+        <v>3.319261976164266e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.372343393698746e-09</v>
+        <v>3.372343393698638e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.589381752024718e-09</v>
+        <v>3.589381752024638e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>2.997200401517121e-09</v>
+        <v>2.99720040151705e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.107615989434587e-09</v>
+        <v>4.107615989434474e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.043444172302026e-09</v>
+        <v>3.043444172302001e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.589276438074217e-09</v>
+        <v>3.589276438074113e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.116676264682325e-09</v>
+        <v>4.116676264682312e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.278821460805704e-08</v>
+        <v>6.278821460805684e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.355640319835302e-08</v>
+        <v>6.355640319835292e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.541082608554582e-08</v>
+        <v>6.541082608554561e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.33131948985228e-08</v>
+        <v>6.331319489852278e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.300886327069394e-08</v>
+        <v>6.30088632706939e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.543140163570745e-08</v>
+        <v>6.543140163570733e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.860635597548572e-08</v>
+        <v>6.860635597548559e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.432620313104722e-08</v>
+        <v>6.432620313104705e-08</v>
       </c>
       <c r="J4" t="n">
         <v>6.831076012699e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.455668412536497e-08</v>
+        <v>6.455668412536476e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.36289599745299e-08</v>
+        <v>6.362895997452967e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.387373965375558e-08</v>
+        <v>6.387373965375551e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.61141252085137e-08</v>
+        <v>6.611412520851355e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.350738956509034e-08</v>
+        <v>6.35073895650902e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.423556804284109e-08</v>
+        <v>6.4235568042841e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.374400408867665e-08</v>
+        <v>6.374400408867671e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.431352061631791e-08</v>
+        <v>6.431352061631772e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.661126511456701e-08</v>
+        <v>6.661126511456687e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.365602248171478e-08</v>
+        <v>6.365602248171469e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.328504423752134e-08</v>
+        <v>6.328504423752118e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.466982828754997e-08</v>
+        <v>8.466982828754986e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>7.911431094457891e-08</v>
+        <v>7.911431094457876e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.730709378206757e-08</v>
+        <v>6.730709378206748e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.395495727424882e-08</v>
+        <v>6.395495727424868e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.466264768213822e-08</v>
+        <v>6.4662647682138e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.918589988936342e-08</v>
+        <v>6.91858998893633e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.247952309653496e-08</v>
+        <v>6.247952309653488e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.228439669599325e-08</v>
+        <v>6.228439669599289e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.251353831902262e-08</v>
+        <v>6.251353831902246e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.247971795476201e-08</v>
+        <v>6.247971795476182e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.232087855084233e-08</v>
+        <v>6.232087855084232e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.227870869267135e-08</v>
+        <v>6.227870869267133e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.252021909012699e-08</v>
+        <v>6.252021909012691e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.247971795476201e-08</v>
+        <v>6.247971795476182e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.247971795476201e-08</v>
+        <v>6.247971795476182e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.53555314009754e-08</v>
+        <v>6.535553140097528e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.247971795476201e-08</v>
+        <v>6.247971795476182e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.247971795476201e-08</v>
+        <v>6.247971795476182e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.243629298365173e-08</v>
+        <v>6.243629298365165e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.232831130254261e-08</v>
+        <v>6.232831130254254e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.236991916494353e-08</v>
+        <v>6.236991916494359e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.235972007251081e-08</v>
+        <v>6.235972007251083e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.224601161079145e-08</v>
+        <v>6.224601161079125e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.247971795476201e-08</v>
+        <v>6.247971795476182e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.247971795476201e-08</v>
+        <v>6.247971795476182e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.247971795476201e-08</v>
+        <v>6.247971795476182e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.238130085406571e-08</v>
+        <v>6.23813008540657e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.172406447493833e-08</v>
+        <v>8.172406447493819e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.247975634046032e-08</v>
+        <v>6.247975634046024e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.226391319194481e-08</v>
+        <v>6.226391319194464e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.26686466345825e-08</v>
+        <v>6.266864663458234e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.22807685033742e-08</v>
+        <v>6.228076850337408e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.247971795476201e-08</v>
+        <v>6.247971795476182e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.265137773073228e-08</v>
+        <v>6.265137773073217e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.110858326197824e-09</v>
+        <v>3.110858326197769e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>3.879046916493882e-09</v>
+        <v>3.879046916493825e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>5.733469803686598e-09</v>
+        <v>5.733469803686541e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>3.635838616663635e-09</v>
+        <v>3.635838616663628e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>3.331506988834763e-09</v>
+        <v>3.331506988834761e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>5.664421270644683e-09</v>
+        <v>5.664421270644557e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.928999693626529e-09</v>
+        <v>8.928999693626467e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.648846849188026e-09</v>
+        <v>4.648846849187956e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>5.645113151447493e-09</v>
+        <v>5.645113151447396e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.879327843505683e-09</v>
+        <v>4.879327843505628e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.951603692670641e-09</v>
+        <v>3.951603692670586e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.196383371896401e-09</v>
+        <v>4.196383371896393e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.436768926654438e-09</v>
+        <v>6.43676892665442e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.740409200027452e-09</v>
+        <v>3.740409200027388e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>4.468587677778244e-09</v>
+        <v>4.468587677778177e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.066647806817445e-09</v>
+        <v>4.066647806817574e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.63616433445867e-09</v>
+        <v>4.636164334458613e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>6.933908832707807e-09</v>
+        <v>6.933908832707733e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>3.978666199855604e-09</v>
+        <v>3.978666199855596e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>3.518063872458444e-09</v>
+        <v>3.51806387245838e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.545786202387624e-09</v>
+        <v>5.545786202387645e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.934733057951602e-08</v>
+        <v>1.934733057951592e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.54011341700473e-09</v>
+        <v>7.540113417004653e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.277600992389616e-09</v>
+        <v>4.277600992389559e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.985291400278954e-09</v>
+        <v>4.98529140027889e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.50854360750422e-09</v>
+        <v>9.508543607504164e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.802166814675754e-09</v>
+        <v>2.80216681467575e-09</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.607040414134004e-09</v>
+        <v>2.607040414133742e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.836182037163463e-09</v>
+        <v>2.836182037163351e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.802361672902818e-09</v>
+        <v>2.802361672902753e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6435222689832e-09</v>
+        <v>2.643522268983194e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.601352410812199e-09</v>
+        <v>2.601352410812196e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.753238725064127e-09</v>
+        <v>2.753238725064099e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.802361672902818e-09</v>
+        <v>2.802361672902753e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.802361672902818e-09</v>
+        <v>2.802361672902753e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.68988442543286e-09</v>
+        <v>2.689884425432731e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.802361672902818e-09</v>
+        <v>2.802361672902753e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.802361672902818e-09</v>
+        <v>2.802361672902753e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.758936701792536e-09</v>
+        <v>2.75893670179253e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.650955020683421e-09</v>
+        <v>2.650955020683431e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.602938799880756e-09</v>
+        <v>2.602938799880773e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.592739707448004e-09</v>
+        <v>2.592739707448017e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.568655328932173e-09</v>
+        <v>2.568655328932155e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.802361672902818e-09</v>
+        <v>2.802361672902753e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.802361672902818e-09</v>
+        <v>2.802361672902753e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.802361672902818e-09</v>
+        <v>2.802361672902753e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.614320489002863e-09</v>
+        <v>2.614320489002893e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.600022389776115e-09</v>
+        <v>2.600022389776071e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.712775975397486e-09</v>
+        <v>2.712775975397478e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.49693282688192e-09</v>
+        <v>2.496932826881879e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.991290352723383e-09</v>
+        <v>2.991290352723222e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.603412221515015e-09</v>
+        <v>2.603412221514929e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.802361672902818e-09</v>
+        <v>2.802361672902753e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.974021448873079e-09</v>
+        <v>2.974021448873074e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.567998596464057e-09</v>
+        <v>4.56799859646399e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.276733427001845e-09</v>
+        <v>5.276733427001846e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.080852442559325e-08</v>
+        <v>1.080852442559315e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>5.277671115788521e-09</v>
+        <v>5.277671115788513e-09</v>
       </c>
       <c r="F2" t="n">
         <v>5.427685017638448e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>9.117227886606313e-09</v>
+        <v>9.117227886606242e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.825345178218761e-08</v>
+        <v>1.825345178218762e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.868195172540374e-09</v>
+        <v>7.868195172540311e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.035169269158615e-08</v>
+        <v>1.035169269158623e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>7.373124405502324e-09</v>
+        <v>7.373124405502255e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>6.123818613101964e-09</v>
+        <v>6.12381861310191e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>8.498336120668682e-09</v>
+        <v>8.498336120668784e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.230322529313185e-08</v>
+        <v>1.230322529313178e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>5.700510161342418e-09</v>
+        <v>5.700510161342355e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>6.252913377428205e-09</v>
+        <v>6.252913377428187e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.835147278096743e-09</v>
+        <v>5.835147278096681e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>6.753276537472373e-09</v>
+        <v>6.753276537472311e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.180823096411702e-08</v>
+        <v>1.180823096411687e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>7.629271955695281e-09</v>
+        <v>7.629271955695213e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>8.475588201518204e-09</v>
+        <v>8.47558820151812e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.463718069312599e-08</v>
+        <v>1.4637180693126e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>4.019464111375304e-08</v>
+        <v>4.019464111375297e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.705746072336378e-08</v>
+        <v>1.705746072336376e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.070422423127363e-09</v>
+        <v>6.070422423127314e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.516948765547452e-09</v>
+        <v>7.516948765547351e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.136011152654622e-08</v>
+        <v>2.13601115265462e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.018473695215965e-09</v>
+        <v>5.018473695215947e-09</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.929014452670855e-09</v>
+        <v>2.929014452670858e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>3.46379077419531e-09</v>
+        <v>3.463790774195305e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>3.427180659314641e-09</v>
+        <v>3.427180659314583e-09</v>
       </c>
       <c r="E3" t="n">
         <v>3.115253726574117e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>2.979457114931349e-09</v>
+        <v>2.979457114931346e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>3.530478667424699e-09</v>
+        <v>3.530478667424661e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>3.427180659314641e-09</v>
+        <v>3.427180659314583e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.427180659314641e-09</v>
+        <v>3.427180659314583e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.40767366306785e-09</v>
+        <v>3.407673663067884e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.427180659314641e-09</v>
+        <v>3.427180659314583e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>3.427180659314641e-09</v>
+        <v>3.427180659314583e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.39412898430983e-09</v>
+        <v>3.394128984309926e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.041018507465206e-09</v>
+        <v>3.041018507465129e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.147139219183151e-09</v>
+        <v>3.147139219182924e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.121126468568137e-09</v>
+        <v>3.121126468568059e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.831113423275919e-09</v>
+        <v>2.831113423275824e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>3.427180659314641e-09</v>
+        <v>3.427180659314583e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>3.427180659314641e-09</v>
+        <v>3.427180659314583e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>3.427180659314641e-09</v>
+        <v>3.427180659314583e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.17550738886952e-09</v>
+        <v>3.175507388869534e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.236003315045157e-09</v>
+        <v>3.236003315045152e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.42727856208307e-09</v>
+        <v>3.427278562082868e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>2.876771345272488e-09</v>
+        <v>2.876771345272493e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.907912196179532e-09</v>
+        <v>3.907912196179401e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.919760759710783e-09</v>
+        <v>2.919760759710781e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.427180659314641e-09</v>
+        <v>3.427180659314583e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.928061908553911e-09</v>
+        <v>3.928061908553906e-09</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.253762562095472e-08</v>
+        <v>6.253762562095456e-08</v>
       </c>
       <c r="C4" t="n">
         <v>6.281921730220556e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.481222400571835e-08</v>
+        <v>6.481222400571807e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.276663478073715e-08</v>
+        <v>6.27666347807371e-08</v>
       </c>
       <c r="F4" t="n">
         <v>6.283370703502027e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.419576627746425e-08</v>
+        <v>6.419576627746397e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.752581260444622e-08</v>
+        <v>6.752581260444604e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.374050852006979e-08</v>
+        <v>6.374050852006967e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.758682529418771e-08</v>
+        <v>6.758682529418757e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.356006103889888e-08</v>
+        <v>6.35600610388986e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.310470374765825e-08</v>
+        <v>6.310470374765813e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.394918276859771e-08</v>
+        <v>6.394918276859772e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.535702492027234e-08</v>
+        <v>6.53570249202722e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.295041278773065e-08</v>
+        <v>6.295041278773052e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.31517572733479e-08</v>
+        <v>6.315175727334782e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.299948643579888e-08</v>
+        <v>6.299948643579869e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.333413376962312e-08</v>
+        <v>6.333413376962291e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.517660529986337e-08</v>
+        <v>6.51766052998632e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.365342381310783e-08</v>
+        <v>6.365342381310767e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.39618961467632e-08</v>
+        <v>6.396189614676294e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.58838011761117e-08</v>
+        <v>8.588380117611174e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>7.552311846934853e-08</v>
+        <v>7.552311846934843e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.708988790754097e-08</v>
+        <v>6.708988790754073e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.308524146342222e-08</v>
+        <v>6.308524146342207e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.361248332926442e-08</v>
+        <v>6.361248332926432e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.865815360102434e-08</v>
+        <v>6.865815360102421e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.268942919786471e-08</v>
+        <v>6.268942919786463e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.19402351464657e-08</v>
+        <v>6.194023514646555e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.215842099390501e-08</v>
+        <v>6.215842099390496e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.212181087902433e-08</v>
+        <v>6.212181087902426e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.197845903475557e-08</v>
+        <v>6.197845903475553e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.194135671302705e-08</v>
+        <v>6.194135671302694e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.215946178999393e-08</v>
+        <v>6.215946178999396e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.212181087902433e-08</v>
+        <v>6.212181087902426e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.212181087902433e-08</v>
+        <v>6.212181087902426e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.505581189908111e-08</v>
+        <v>6.505581189908094e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.212181087902433e-08</v>
+        <v>6.212181087902426e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.212181087902433e-08</v>
+        <v>6.212181087902426e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.208875920402109e-08</v>
+        <v>6.20887592040211e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.198105930922008e-08</v>
+        <v>6.198105930921985e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.201973906250885e-08</v>
+        <v>6.201973906250888e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.201025772036703e-08</v>
+        <v>6.20102577203668e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.190455137086313e-08</v>
+        <v>6.190455137086292e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.212181087902433e-08</v>
+        <v>6.212181087902426e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.212181087902433e-08</v>
+        <v>6.212181087902426e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.212181087902433e-08</v>
+        <v>6.212181087902426e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.203007892724387e-08</v>
+        <v>6.203007892724375e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.172820590118526e-08</v>
+        <v>8.172820590118524e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.212184656343372e-08</v>
+        <v>6.212184656343363e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.192119314728852e-08</v>
+        <v>6.192119314728831e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.229703187917685e-08</v>
+        <v>6.229703187917671e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.193686228404402e-08</v>
+        <v>6.193686228404393e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.212181087902433e-08</v>
+        <v>6.212181087902426e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.229198690588803e-08</v>
+        <v>6.229198690588796e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.113063696258117e-09</v>
+        <v>3.113063696257916e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3946553775088e-09</v>
+        <v>3.394655377508795e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>5.387662081021676e-09</v>
+        <v>5.387662081021462e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>3.342072856040456e-09</v>
+        <v>3.34207285604045e-09</v>
       </c>
       <c r="F6" t="n">
         <v>3.409145110323566e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.686282700156765e-09</v>
+        <v>4.686282700156716e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.101250679749526e-09</v>
+        <v>8.101250679749343e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.315946595373191e-09</v>
+        <v>4.315946595372991e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>5.127159304249113e-09</v>
+        <v>5.127159304249068e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.135499114202276e-09</v>
+        <v>4.135499114202013e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.680141822961624e-09</v>
+        <v>3.680141822961424e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.524620843900907e-09</v>
+        <v>4.524620843900989e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>5.932462995575763e-09</v>
+        <v>5.932462995575563e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.440929210423253e-09</v>
+        <v>3.440929210423171e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>3.642273696040457e-09</v>
+        <v>3.642273696040394e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.574924511102171e-09</v>
+        <v>3.574924511101972e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>3.909571844926503e-09</v>
+        <v>3.909571844926302e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>5.752043375166724e-09</v>
+        <v>5.752043375166474e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.228861888411216e-09</v>
+        <v>4.228861888411015e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.452412569455741e-09</v>
+        <v>4.45241256945563e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>6.674301193112885e-09</v>
+        <v>6.674301193112884e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.601363489204116e-08</v>
+        <v>1.601363489204106e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.580404330233541e-09</v>
+        <v>7.580404330233401e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.660679538725598e-09</v>
+        <v>3.660679538725372e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.187921404567764e-09</v>
+        <v>4.187921404567605e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.233591676327705e-09</v>
+        <v>9.23359167632749e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.264867273167986e-09</v>
+        <v>3.264867273167966e-09</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.515673221768886e-09</v>
+        <v>2.515673221768863e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.733859069208263e-09</v>
+        <v>2.73385906920826e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.697248954327525e-09</v>
+        <v>2.697248954327537e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.553897110058797e-09</v>
+        <v>2.553897110058796e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.516794788330315e-09</v>
+        <v>2.516794788330313e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.649978212686506e-09</v>
+        <v>2.649978212686562e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.697248954327525e-09</v>
+        <v>2.697248954327537e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.697248954327525e-09</v>
+        <v>2.697248954327537e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.596145909142438e-09</v>
+        <v>2.596145909142409e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.697248954327525e-09</v>
+        <v>2.697248954327537e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.697248954327525e-09</v>
+        <v>2.697248954327537e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.664197279324371e-09</v>
+        <v>2.664197279324451e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.556497384523439e-09</v>
+        <v>2.556497384523271e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.510255485201498e-09</v>
+        <v>2.510255485201495e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.50077414305964e-09</v>
+        <v>2.500774143059511e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.479989446166337e-09</v>
+        <v>2.479989446166264e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.697248954327525e-09</v>
+        <v>2.697248954327537e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.697248954327525e-09</v>
+        <v>2.697248954327537e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.697248954327525e-09</v>
+        <v>2.697248954327537e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.520595349936418e-09</v>
+        <v>2.520595349936311e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.518705918186477e-09</v>
+        <v>2.518705918186473e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.612362986126276e-09</v>
+        <v>2.612362986126254e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.411709569981087e-09</v>
+        <v>2.411709569980922e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.872469954480199e-09</v>
+        <v>2.872469954480048e-09</v>
       </c>
       <c r="Z7" t="n">
         <v>2.512300359347245e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.697248954327525e-09</v>
+        <v>2.697248954327537e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.867424981191326e-09</v>
+        <v>2.867424981191305e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.069072650520005e-08</v>
+        <v>1.069072650520076e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.419247851680419e-09</v>
+        <v>6.419247851681871e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>2.791494664660142e-08</v>
+        <v>2.791494664660212e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>8.516200713877011e-09</v>
+        <v>8.516200713877357e-09</v>
       </c>
       <c r="F2" t="n">
         <v>1.61669216347176e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>5.903552683186365e-09</v>
+        <v>5.90355268318709e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.555142862496007e-08</v>
+        <v>2.555142862496077e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.617149113961282e-08</v>
+        <v>3.617149113961333e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.549902011816203e-08</v>
+        <v>1.549902011816229e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.090370506215614e-08</v>
+        <v>6.09037050621568e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.51305895852819e-09</v>
+        <v>8.513058958528875e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>8.83701519861103e-09</v>
+        <v>8.837015198611041e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>6.502295700388202e-08</v>
+        <v>6.502295700388263e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.403459424319487e-08</v>
+        <v>1.40345942431955e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.543073605846705e-08</v>
+        <v>1.543073605846749e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.457253801505058e-08</v>
+        <v>2.457253801505117e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>2.022337440385635e-08</v>
+        <v>2.02233744038562e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.914571157119519e-08</v>
+        <v>1.914571157119582e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>2.497759509557296e-08</v>
+        <v>2.49775950955736e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.368918240479014e-08</v>
+        <v>1.368918240479093e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36900151083004e-08</v>
+        <v>1.369001510830037e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>6.128038976965986e-08</v>
+        <v>6.128038976966054e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>2.257749569872177e-08</v>
+        <v>2.257749569872242e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.925690643005392e-08</v>
+        <v>1.925690643005452e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.297000149453792e-08</v>
+        <v>1.297000149453853e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.475018238991843e-08</v>
+        <v>1.475018238991895e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.080268714771298e-09</v>
+        <v>8.080268714771305e-09</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.503153553147001e-09</v>
+        <v>3.503153553147915e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.205399628881068e-09</v>
+        <v>4.205399628881391e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.185825960771124e-09</v>
+        <v>4.185825960771702e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.747796913964434e-09</v>
+        <v>3.74779691396475e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.591434887395911e-09</v>
+        <v>3.591434887395917e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.327382531510371e-09</v>
+        <v>4.327382531510652e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.185825960771124e-09</v>
+        <v>4.185825960771702e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.185825960771124e-09</v>
+        <v>4.185825960771702e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.150240424130653e-09</v>
+        <v>4.150240424130876e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.185825960771124e-09</v>
+        <v>4.185825960771702e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.185825960771124e-09</v>
+        <v>4.185825960771702e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.124598912591406e-09</v>
+        <v>4.124598912591412e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65664063565904e-09</v>
+        <v>3.656640635659565e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.802065356662602e-09</v>
+        <v>3.802065356662894e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.766418243714422e-09</v>
+        <v>3.766418243715276e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.368992844411013e-09</v>
+        <v>3.368992844411116e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.185825960771124e-09</v>
+        <v>4.185825960771702e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.185825960771124e-09</v>
+        <v>4.185825960771702e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.185825960771124e-09</v>
+        <v>4.185825960771702e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.852210609569411e-09</v>
+        <v>3.852210609569579e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.917165396375422e-09</v>
+        <v>3.917165396375531e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.185960123179813e-09</v>
+        <v>4.185960123180745e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.431561125661406e-09</v>
+        <v>3.431561125662427e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.863886683026618e-09</v>
+        <v>4.863886683027051e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.490472562874533e-09</v>
+        <v>3.490472562874721e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.185825960771124e-09</v>
+        <v>4.185825960771702e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.862119195898768e-09</v>
+        <v>4.862119195898778e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.558330707112611e-08</v>
+        <v>6.558330707112728e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.403884255608228e-08</v>
+        <v>6.403884255608359e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.186133305566241e-08</v>
+        <v>7.186133305566387e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.474335572543335e-08</v>
+        <v>6.47433557254338e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.756783152788569e-08</v>
+        <v>6.756783152788592e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.383843842683542e-08</v>
+        <v>6.38384384268362e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.099985849060408e-08</v>
+        <v>7.099985849060498e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.487074657012476e-08</v>
+        <v>7.487074657012593e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.027577128278631e-08</v>
+        <v>7.027577128278639e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.388534812457323e-08</v>
+        <v>8.388534812457425e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.478957282182752e-08</v>
+        <v>6.478957282182856e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.486874055916771e-08</v>
+        <v>6.486874055916818e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.538676708663394e-08</v>
+        <v>8.538676708663484e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.680210759594784e-08</v>
+        <v>6.680210759594875e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.73109848932897e-08</v>
+        <v>6.731098489329063e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.064306435800602e-08</v>
+        <v>7.064306435800695e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.905784529218324e-08</v>
+        <v>6.905784529218416e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.866504984423412e-08</v>
+        <v>6.866504984423504e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>7.079070290743598e-08</v>
+        <v>7.079070290743692e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.667620903687985e-08</v>
+        <v>6.667620903688086e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.638978590762032e-08</v>
+        <v>8.638978590762016e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>8.402264527720321e-08</v>
+        <v>8.402264527720461e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.991589486067385e-08</v>
+        <v>6.991589486067472e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.870557906457217e-08</v>
+        <v>6.870557906457333e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.641407604014158e-08</v>
+        <v>6.641407604014273e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.70629310725683e-08</v>
+        <v>6.706293107256948e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.460842938297499e-08</v>
+        <v>6.460842938297531e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.296352113084559e-08</v>
+        <v>6.296352113084699e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.323192087519067e-08</v>
+        <v>6.323192087519119e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.321234720708054e-08</v>
+        <v>6.321234720708137e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.300532853378957e-08</v>
+        <v>6.300532853379042e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.298421427730775e-08</v>
+        <v>6.298421427730788e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.326394291487374e-08</v>
+        <v>6.326394291487485e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.321234720708054e-08</v>
+        <v>6.321234720708137e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.321234720708054e-08</v>
+        <v>6.321234720708137e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.613927434841128e-08</v>
+        <v>6.613927434841219e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.321234720708054e-08</v>
+        <v>6.321234720708137e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.321234720708054e-08</v>
+        <v>6.321234720708137e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.315112015889939e-08</v>
+        <v>6.315112015889963e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.301946537008497e-08</v>
+        <v>6.301946537008572e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.307247097322751e-08</v>
+        <v>6.307247097322759e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.30594780191474e-08</v>
+        <v>6.305947801914819e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.291462112790593e-08</v>
+        <v>6.291462112790706e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.321234720708054e-08</v>
+        <v>6.321234720708137e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.321234720708054e-08</v>
+        <v>6.321234720708137e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.321234720708054e-08</v>
+        <v>6.321234720708137e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.309074832907673e-08</v>
+        <v>6.309074832907805e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.28276969462188e-08</v>
+        <v>8.282769694621894e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.321239610770301e-08</v>
+        <v>6.321239610770409e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.293742653170797e-08</v>
+        <v>6.293742653170947e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.345949237815165e-08</v>
+        <v>6.345949237815185e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.295889905879906e-08</v>
+        <v>6.295889905880038e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.321234720708054e-08</v>
+        <v>6.321234720708137e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.343545167276547e-08</v>
+        <v>6.343545167276594e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.546003535147774e-09</v>
+        <v>5.546003535148587e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>4.001539020104623e-09</v>
+        <v>4.001539020104843e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.182402951968414e-08</v>
+        <v>1.182402951968498e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.706052189454962e-09</v>
+        <v>4.706052189455228e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>7.530527991907283e-09</v>
+        <v>7.530527991907287e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.695265958515032e-09</v>
+        <v>3.695265958515635e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.096255495462573e-08</v>
+        <v>1.096255495462642e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.483344303414644e-08</v>
+        <v>1.483344303414715e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.174194765430779e-09</v>
+        <v>7.174194765431317e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>2.384804458859491e-08</v>
+        <v>2.384804458859551e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.752269285849319e-09</v>
+        <v>4.75226928584996e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.831437023189351e-09</v>
+        <v>4.831437023189356e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.534946355065556e-08</v>
+        <v>2.534946355065622e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>6.658935127627439e-09</v>
+        <v>6.658935127628188e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>7.167812424969232e-09</v>
+        <v>7.167812424969655e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.060576082202762e-08</v>
+        <v>1.060576082202834e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>9.020541756204882e-09</v>
+        <v>9.02054175620568e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>8.627746308255777e-09</v>
+        <v>8.62774630825643e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.075339937145766e-08</v>
+        <v>1.075339937145836e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.533036568559456e-09</v>
+        <v>6.533036568560006e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>6.487672652077231e-09</v>
+        <v>6.487672652077186e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.387947280888278e-08</v>
+        <v>2.387947280888379e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>9.772722392353384e-09</v>
+        <v>9.772722392354208e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.668275528593826e-09</v>
+        <v>8.668275528594522e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.376772504163226e-09</v>
+        <v>6.37677250416393e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.02562753658997e-09</v>
+        <v>7.025627536590683e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.571125846996596e-09</v>
+        <v>4.571125846996604e-09</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.926217594867233e-09</v>
+        <v>2.926217594868173e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>3.194617339212046e-09</v>
+        <v>3.194617339212397e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>3.175043671102143e-09</v>
+        <v>3.175043671102731e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.968024997811234e-09</v>
+        <v>2.968024997811491e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.946910741329401e-09</v>
+        <v>2.946910741329406e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>3.12077044655334e-09</v>
+        <v>3.120770446554259e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>3.175043671102143e-09</v>
+        <v>3.175043671102731e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>3.175043671102143e-09</v>
+        <v>3.175043671102731e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>3.037697831055762e-09</v>
+        <v>3.037697831056168e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.175043671102143e-09</v>
+        <v>3.175043671102731e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>3.175043671102143e-09</v>
+        <v>3.175043671102731e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>3.113816622921021e-09</v>
+        <v>3.113816622921026e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.982161834106625e-09</v>
+        <v>2.982161834107119e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.929298504907051e-09</v>
+        <v>2.929298504907118e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.916305550826937e-09</v>
+        <v>2.916305550827482e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.877317591927602e-09</v>
+        <v>2.877317591928262e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>3.175043671102143e-09</v>
+        <v>3.175043671102731e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>3.175043671102143e-09</v>
+        <v>3.175043671102731e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>3.175043671102143e-09</v>
+        <v>3.175043671102731e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.947575860756297e-09</v>
+        <v>2.947575860757066e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.925583690675895e-09</v>
+        <v>2.925583690675834e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>3.069223639382656e-09</v>
+        <v>3.069223639383547e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.79425406338748e-09</v>
+        <v>2.794254063388468e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.422188842173263e-09</v>
+        <v>3.422188842173402e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.921595522820649e-09</v>
+        <v>2.921595522821578e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.175043671102143e-09</v>
+        <v>3.175043671102731e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.398148136787113e-09</v>
+        <v>3.398148136787126e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6742,85 +6742,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.996101796442655e-09</v>
+        <v>4.996101796442672e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>8.021085260032327e-09</v>
+        <v>8.02108526003232e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.155144409571237e-08</v>
+        <v>1.155144409571238e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.413898820403813e-09</v>
+        <v>9.413898820403829e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>4.365869979442311e-09</v>
+        <v>4.36586997944231e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.025168910994952e-08</v>
+        <v>1.025168910994954e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.146841167957207e-08</v>
+        <v>2.146841167957209e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>8.211762512480852e-09</v>
+        <v>8.211762512480875e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.237472536451301e-08</v>
+        <v>1.237472536451297e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.427684018463637e-08</v>
+        <v>1.427684018463638e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.220338783810496e-09</v>
+        <v>7.22033878381051e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>7.188825417863451e-09</v>
+        <v>7.188825417863448e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.916798662841103e-08</v>
+        <v>1.916798662841105e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>5.305870538033069e-09</v>
+        <v>5.305870538033089e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.528473428204606e-08</v>
+        <v>1.528473428204605e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.316846417242468e-08</v>
+        <v>1.31684641724247e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.002499525600784e-08</v>
+        <v>1.002499525600787e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.516174829554013e-08</v>
+        <v>1.516174829554015e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>7.110082899071492e-09</v>
+        <v>7.1100828990715e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>6.691314582005642e-09</v>
+        <v>6.69131458200567e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.253034608239497e-08</v>
+        <v>1.253034608239496e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>5.939756214463567e-08</v>
+        <v>5.939756214463566e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.880211595096203e-08</v>
+        <v>1.880211595096204e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.079343628643107e-08</v>
+        <v>1.079343628643108e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.000833747699587e-08</v>
+        <v>1.000833747699588e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.23363828874144e-08</v>
+        <v>1.233638288741441e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.229874458565378e-08</v>
+        <v>1.229874458565377e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6830,13 +6830,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.187004141297284e-09</v>
+        <v>3.187004141297302e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>3.806719969298158e-09</v>
+        <v>3.806719969298155e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>3.769697481082121e-09</v>
+        <v>3.769697481082138e-09</v>
       </c>
       <c r="E3" t="n">
         <v>3.407295446949283e-09</v>
@@ -6845,70 +6845,70 @@
         <v>3.237180211115351e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>3.890522740845878e-09</v>
+        <v>3.890522740845897e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>3.769697481082121e-09</v>
+        <v>3.769697481082138e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.769697481082121e-09</v>
+        <v>3.769697481082138e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.742531359310523e-09</v>
+        <v>3.742531359310533e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.769697481082121e-09</v>
+        <v>3.769697481082138e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>3.769697481082121e-09</v>
+        <v>3.769697481082138e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.722968724604853e-09</v>
+        <v>3.722968724604855e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.318012659819558e-09</v>
+        <v>3.318012659819575e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.442139569715754e-09</v>
+        <v>3.44213956971577e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.411713064866639e-09</v>
+        <v>3.411713064866666e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.07249160116083e-09</v>
+        <v>3.072491601160854e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>3.769697481082121e-09</v>
+        <v>3.769697481082138e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>3.769697481082121e-09</v>
+        <v>3.769697481082138e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>3.769697481082121e-09</v>
+        <v>3.769697481082138e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.47977541149031e-09</v>
+        <v>3.479775411490322e-09</v>
       </c>
       <c r="V3" t="n">
         <v>3.541314294582306e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.769811995275342e-09</v>
+        <v>3.769811995275367e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.12589660251301e-09</v>
+        <v>3.125896602513022e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.339617836047938e-09</v>
+        <v>4.339617836047959e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.176180313497458e-09</v>
+        <v>3.176180313497475e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.769697481082121e-09</v>
+        <v>3.769697481082138e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.374066791171783e-09</v>
+        <v>4.374066791171786e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6921,82 +6921,82 @@
         <v>6.313173018388562e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.425782936121614e-08</v>
+        <v>6.42578293612161e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.552107547525372e-08</v>
+        <v>6.552107547525371e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.470883290568639e-08</v>
+        <v>6.470883290568631e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.287621583869855e-08</v>
+        <v>6.28762158386985e-08</v>
       </c>
       <c r="G4" t="n">
         <v>6.504733004543679e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.913569370865785e-08</v>
+        <v>6.913569370865793e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.430380075468695e-08</v>
+        <v>6.430380075468697e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.873445917044042e-08</v>
+        <v>6.873445917044046e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.65144503464499e-08</v>
+        <v>6.651445034644994e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.394243844747181e-08</v>
+        <v>6.394243844747185e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.390125552217274e-08</v>
+        <v>6.390125552217269e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.829721579046447e-08</v>
+        <v>6.829721579046456e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.324463725270711e-08</v>
+        <v>6.324463725270713e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.688181590966571e-08</v>
+        <v>6.688181590966579e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.611046030520699e-08</v>
+        <v>6.611046030520706e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.496470279764868e-08</v>
+        <v>6.496470279764877e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.68369889617586e-08</v>
+        <v>6.683698896175865e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.390225147217438e-08</v>
+        <v>6.390225147217446e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.374961533802978e-08</v>
+        <v>6.374961533802981e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.538985449050631e-08</v>
+        <v>8.538985449050628e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>8.296042366660214e-08</v>
+        <v>8.296042366660218e-08</v>
       </c>
       <c r="X4" t="n">
         <v>6.816386022480468e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.524479052974779e-08</v>
+        <v>6.524479052974783e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.495863123280436e-08</v>
+        <v>6.49586312328044e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.580717644761247e-08</v>
+        <v>6.580717644761249e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.579072337212299e-08</v>
+        <v>6.579072337212293e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7006,22 +7006,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.247233533208235e-08</v>
+        <v>6.247233533208233e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.272174270031927e-08</v>
+        <v>6.272174270031925e-08</v>
       </c>
       <c r="D5" t="n">
         <v>6.268472021210327e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.251949650916006e-08</v>
+        <v>6.251949650916009e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.246482167188775e-08</v>
+        <v>6.246482167188779e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.272875960048538e-08</v>
+        <v>6.272875960048532e-08</v>
       </c>
       <c r="H5" t="n">
         <v>6.268472021210327e-08</v>
@@ -7030,7 +7030,7 @@
         <v>6.268472021210327e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.558812581988379e-08</v>
+        <v>6.55881258198839e-08</v>
       </c>
       <c r="K5" t="n">
         <v>6.268472021210327e-08</v>
@@ -7039,19 +7039,19 @@
         <v>6.268472021210327e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2637991455624e-08</v>
+        <v>6.263799145562396e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.252008639870405e-08</v>
+        <v>6.252008639870399e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.256532919978942e-08</v>
+        <v>6.256532919978943e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.255423909605797e-08</v>
+        <v>6.255423909605801e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.243059685587667e-08</v>
+        <v>6.243059685587675e-08</v>
       </c>
       <c r="R5" t="n">
         <v>6.268472021210327e-08</v>
@@ -7063,19 +7063,19 @@
         <v>6.268472021210327e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.257904702217382e-08</v>
+        <v>6.257904702217385e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.211345795838908e-08</v>
+        <v>8.211345795838903e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.268476195118192e-08</v>
+        <v>6.268476195118198e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.245006235175643e-08</v>
+        <v>6.245006235175642e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.289244948914558e-08</v>
+        <v>6.28924494891456e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>6.246839017394912e-08</v>
@@ -7094,85 +7094,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.358287542783039e-09</v>
+        <v>3.358287542783057e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>4.484386720113567e-09</v>
+        <v>4.484386720113562e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>5.747632834151189e-09</v>
+        <v>5.747632834151201e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>4.935390264583773e-09</v>
+        <v>4.935390264583776e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>3.102773197595923e-09</v>
+        <v>3.102773197595922e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>5.179192434291498e-09</v>
+        <v>5.179192434291516e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>9.362251067555325e-09</v>
+        <v>9.362251067555336e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.530358113584408e-09</v>
+        <v>4.530358113584422e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>5.939400528911652e-09</v>
+        <v>5.939400528911673e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>6.741007705347333e-09</v>
+        <v>6.741007705347348e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.168995806369262e-09</v>
+        <v>4.168995806369275e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.127812881070129e-09</v>
+        <v>4.12781288107013e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>8.5237731493619e-09</v>
+        <v>8.523773149361938e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.376499641561793e-09</v>
+        <v>3.376499641561815e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>7.013678298520383e-09</v>
+        <v>7.01367829852041e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.337017664104419e-09</v>
+        <v>6.337017664104434e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>5.191260156546135e-09</v>
+        <v>5.191260156546146e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>7.063546320656092e-09</v>
+        <v>7.063546320656107e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.128808831071847e-09</v>
+        <v>4.128808831071879e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>3.881477726884457e-09</v>
+        <v>3.881477726884484e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.975162400517221e-09</v>
+        <v>5.975162400517226e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.309228605545689e-08</v>
+        <v>2.309228605545693e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>8.295722613659398e-09</v>
+        <v>8.295722613659418e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.471347888645242e-09</v>
+        <v>5.471347888645262e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.185188591701789e-09</v>
+        <v>5.185188591701796e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.03373380650993e-09</v>
+        <v>6.033733806509943e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.017280731020404e-09</v>
+        <v>6.017280731020398e-09</v>
       </c>
     </row>
     <row r="7">
@@ -7182,82 +7182,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.698892690979775e-09</v>
+        <v>2.698892690979776e-09</v>
       </c>
       <c r="C7" t="n">
         <v>2.948300059216727e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9112775710007e-09</v>
+        <v>2.911277571000702e-09</v>
       </c>
       <c r="E7" t="n">
         <v>2.74605386805747e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.691379030785157e-09</v>
+        <v>2.691379030785158e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.860621989340001e-09</v>
+        <v>2.860621989340017e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9112775710007e-09</v>
+        <v>2.911277571000702e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9112775710007e-09</v>
+        <v>2.911277571000702e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.793067178355054e-09</v>
+        <v>2.793067178355062e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9112775710007e-09</v>
+        <v>2.911277571000702e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9112775710007e-09</v>
+        <v>2.911277571000702e-09</v>
       </c>
       <c r="M7" t="n">
         <v>2.864548814521426e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.746643757601455e-09</v>
+        <v>2.746643757601449e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.697191588644096e-09</v>
+        <v>2.697191588644109e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.686101484912653e-09</v>
+        <v>2.686101484912669e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.657154214774171e-09</v>
+        <v>2.657154214774177e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9112775710007e-09</v>
+        <v>2.911277571000702e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9112775710007e-09</v>
+        <v>2.911277571000702e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9112775710007e-09</v>
+        <v>2.911277571000702e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.710909411028557e-09</v>
+        <v>2.710909411028566e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.698765868399984e-09</v>
+        <v>2.698765868399986e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.816624340036684e-09</v>
+        <v>2.816624340036698e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.581924740611092e-09</v>
+        <v>2.581924740611116e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.119006848043052e-09</v>
+        <v>3.119006848043049e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.694947532846532e-09</v>
+        <v>2.694947532846542e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.9112775710007e-09</v>
+        <v>2.911277571000702e-09</v>
       </c>
       <c r="AB7" t="n">
         <v>3.128828731196589e-09</v>
